--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srb\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1400EBC1-2B16-45FC-AD1D-965A61A25EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="1950" yWindow="825" windowWidth="21870" windowHeight="19545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="List1" sheetId="1" r:id="rId1"/>
+    <sheet name="Útok" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,8 +24,262 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="83">
+  <si>
+    <t>attack_type</t>
+  </si>
+  <si>
+    <t>severity</t>
+  </si>
+  <si>
+    <t>effect</t>
+  </si>
+  <si>
+    <t>roleplay_1</t>
+  </si>
+  <si>
+    <t>roleplay_2</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>Melee</t>
+  </si>
+  <si>
+    <t>Lehký</t>
+  </si>
+  <si>
+    <t>Nevýhoda na další útok.</t>
+  </si>
+  <si>
+    <t>Tvůj švih mine o vlásek, soupeř v poslední chvíli ucukne.</t>
+  </si>
+  <si>
+    <t>Musíš znovu srovnat postoj, než se odvážíš k dalšímu úderu.</t>
+  </si>
+  <si>
+    <t>Ztratíš reakci do začátku dalšího kola.</t>
+  </si>
+  <si>
+    <t>Tvůj útok tě vyvede z rytmu a nestíháš reagovat na pohyb soupeře.</t>
+  </si>
+  <si>
+    <t>Na okamžik se soustředíš jen na to, abys znovu nabyl rovnováhu.</t>
+  </si>
+  <si>
+    <t>Cíl má výhodu na první útok proti tobě.</t>
+  </si>
+  <si>
+    <t>Tvůj postoj zůstane otevřený a dáváš soupeři příležitost.</t>
+  </si>
+  <si>
+    <t>Vidíš, že přesně ví, kdy proti tobě zaútočit.</t>
+  </si>
+  <si>
+    <t>Nemůžeš provádět příležitostné útoky do začátku dalšího kola.</t>
+  </si>
+  <si>
+    <t>Tvůj pohyb je rozházený a nestíháš hlídat okolí.</t>
+  </si>
+  <si>
+    <t>Soupeři kolem tebe mají větší prostor k manévrování.</t>
+  </si>
+  <si>
+    <t>Tvůj pohyb je snížen o 3 m do konce příštího kola.</t>
+  </si>
+  <si>
+    <t>Špatně došlápneš a noha tě na okamžik neposlouchá.</t>
+  </si>
+  <si>
+    <t>Každý další krok vyžaduje větší opatrnost.</t>
+  </si>
+  <si>
+    <t>Nemůžeš použít bonusovou akci do konce kola.</t>
+  </si>
+  <si>
+    <t>Musíš vložit všechnu pozornost do dokončení útoku.</t>
+  </si>
+  <si>
+    <t>Na další manévry ti v tuto chvíli nezbývá prostor.</t>
+  </si>
+  <si>
+    <t>Tvůj další útok nemůže mít výhodu.</t>
+  </si>
+  <si>
+    <t>Tvůj rytmus boje je narušený.</t>
+  </si>
+  <si>
+    <t>Ani při dobré příležitosti se nedokážeš opřít o převahu.</t>
+  </si>
+  <si>
+    <t>Máš -2 k AC do začátku dalšího kola.</t>
+  </si>
+  <si>
+    <t>Tvůj postoj je otevřený a obrana oslabená.</t>
+  </si>
+  <si>
+    <t>Soupeř si tvé chyby okamžitě všimne.</t>
+  </si>
+  <si>
+    <t>Nemůžeš použít Weapon Mastery při dalším útoku.</t>
+  </si>
+  <si>
+    <t>Zbraň se ti v ruce nechová tak, jak bys chtěl.</t>
+  </si>
+  <si>
+    <t>Na precizní techniky si budeš muset počkat.</t>
+  </si>
+  <si>
+    <t>Tvůj další útok nemůže kriticky zasáhnout.</t>
+  </si>
+  <si>
+    <t>Tvůj úder postrádá přesnost i načasování.</t>
+  </si>
+  <si>
+    <t>I dobře mířený zásah nemá rozhodující sílu.</t>
+  </si>
+  <si>
+    <t>Máš nevýhodu na Athletics do konce příštího kola.</t>
+  </si>
+  <si>
+    <t>Svaly nemáš ve správném napětí.</t>
+  </si>
+  <si>
+    <t>Silové manévry ti teď půjdou hůř než obvykle.</t>
+  </si>
+  <si>
+    <t>Máš nevýhodu na Acrobatics do konce příštího kola.</t>
+  </si>
+  <si>
+    <t>Tvůj pohyb je nejistý a neohrabaný.</t>
+  </si>
+  <si>
+    <t>Rychlé obraty jsou teď nebezpečné.</t>
+  </si>
+  <si>
+    <t>Nemůžeš použít Disengage do konce příštího kola.</t>
+  </si>
+  <si>
+    <t>Soupeř tě drží pod tlakem a nedává ti prostor ustoupit.</t>
+  </si>
+  <si>
+    <t>Jakýkoli pokus o únik by byl riskantní.</t>
+  </si>
+  <si>
+    <t>Nemůžeš použít Dodge do konce příštího kola.</t>
+  </si>
+  <si>
+    <t>Stále jsi soustředěný na předchozí útok.</t>
+  </si>
+  <si>
+    <t>Na čistou obranu se teď nedokážeš plně zaměřit.</t>
+  </si>
+  <si>
+    <t>Tvůj další útok má snížený dosah o 1,5 m.</t>
+  </si>
+  <si>
+    <t>Tvůj krok vpřed není dostatečně jistý.</t>
+  </si>
+  <si>
+    <t>Musíš se k cíli přiblížit víc, než jsi plánoval.</t>
+  </si>
+  <si>
+    <t>Nemůžeš použít Ready akci do konce příštího kola.</t>
+  </si>
+  <si>
+    <t>Tvůj bojový rytmus je narušený.</t>
+  </si>
+  <si>
+    <t>Nestíháš se připravit na reakční útok.</t>
+  </si>
+  <si>
+    <t>Tvůj další útok nemůže využít flanking.</t>
+  </si>
+  <si>
+    <t>Špatné načasování tě vyvede z ideální pozice.</t>
+  </si>
+  <si>
+    <t>Se spojenci se na chvíli nedokážeš sladit.</t>
+  </si>
+  <si>
+    <t>Tvůj pohyb vyvolá příležitostný útok, pokud se pohneš.</t>
+  </si>
+  <si>
+    <t>Tvůj postoj je příliš otevřený.</t>
+  </si>
+  <si>
+    <t>Jakýkoli krok může dát soupeři šanci zaútočit.</t>
+  </si>
+  <si>
+    <t>Tvůj další útok nemůže využít magický bonus zbraně.</t>
+  </si>
+  <si>
+    <t>Magie ve zbrani na okamžik pohasne.</t>
+  </si>
+  <si>
+    <t>Musíš se spolehnout jen na vlastní sílu.</t>
+  </si>
+  <si>
+    <t>Nemůžeš použít reroll mechaniky při dalším útoku.</t>
+  </si>
+  <si>
+    <t>Štěstí se od tebe na chvíli odvrací.</t>
+  </si>
+  <si>
+    <t>Musíš přijmout výsledek takový, jaký je.</t>
+  </si>
+  <si>
+    <t>Tvůj další útok automaticky mine při hodu 1–2.</t>
+  </si>
+  <si>
+    <t>Tvé pohyby jsou stále nejisté.</t>
+  </si>
+  <si>
+    <t>Stačí drobná chyba a útok zcela selže.</t>
+  </si>
+  <si>
+    <t>Nemůžeš použít Extra Attack při dalším útoku.</t>
+  </si>
+  <si>
+    <t>Předchozí výpad tě zcela vyčerpal.</t>
+  </si>
+  <si>
+    <t>Na rychlou kombinaci teď nemáš prostor.</t>
+  </si>
+  <si>
+    <t>Tvůj další útok má minimální možné poškození.</t>
+  </si>
+  <si>
+    <t>Úder sice zasáhne, ale bez potřebné síly.</t>
+  </si>
+  <si>
+    <t>Soupeř zásah téměř ignoruje.</t>
+  </si>
+  <si>
+    <t>Nemůžeš použít class feature při dalším útoku.</t>
+  </si>
+  <si>
+    <t>Tvá technika selhává v klíčový moment.</t>
+  </si>
+  <si>
+    <t>Musíš se spolehnout jen na základní instinkt.</t>
+  </si>
+  <si>
+    <t>Tvůj pohyb je považován za obtížný terén do konce kola.</t>
+  </si>
+  <si>
+    <t>Každý krok je těžší, než by měl být.</t>
+  </si>
+  <si>
+    <t>Bojiště ti klade odpor.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -53,7 +313,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +590,534 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="6" width="12.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srb\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1400EBC1-2B16-45FC-AD1D-965A61A25EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4FBA3E-F5B5-4A1A-B5E5-4A48064ED6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="825" windowWidth="21870" windowHeight="19545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2295" yWindow="1170" windowWidth="21870" windowHeight="19545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Útok" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="84">
   <si>
     <t>attack_type</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>Bojiště ti klade odpor.</t>
+  </si>
+  <si>
+    <t>dada</t>
   </si>
 </sst>
 </file>
@@ -591,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="12.85546875" customWidth="1"/>
@@ -1117,6 +1120,11 @@
         <v>1</v>
       </c>
     </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srb\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4FBA3E-F5B5-4A1A-B5E5-4A48064ED6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F113E60D-95E3-4076-AC34-45612B5C39B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2295" yWindow="1170" windowWidth="21870" windowHeight="19545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="88">
   <si>
     <t>attack_type</t>
   </si>
@@ -276,7 +276,19 @@
     <t>Bojiště ti klade odpor.</t>
   </si>
   <si>
-    <t>dada</t>
+    <t>Ranged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lehký </t>
+  </si>
+  <si>
+    <t>bla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bla </t>
+  </si>
+  <si>
+    <t xml:space="preserve">smrdíš </t>
   </si>
 </sst>
 </file>
@@ -1124,6 +1136,21 @@
       <c r="A27" t="s">
         <v>83</v>
       </c>
+      <c r="B27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" t="s">
+        <v>87</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srb\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F113E60D-95E3-4076-AC34-45612B5C39B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B156D3-023C-4FDB-ACD2-C2CAB654EF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="1170" windowWidth="21870" windowHeight="19545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2295" yWindow="1170" windowWidth="21870" windowHeight="19545" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Útok" sheetId="1" r:id="rId1"/>
+    <sheet name="Obrana" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="88">
   <si>
     <t>attack_type</t>
   </si>
@@ -1155,4 +1156,476 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80CAE411-9ABA-4D2F-A12C-49D9B350EB7D}">
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="5" width="12.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" t="s">
+        <v>78</v>
+      </c>
+      <c r="D25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srb\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B156D3-023C-4FDB-ACD2-C2CAB654EF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A97CEC-6689-483C-8787-1A2C3AC79423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="1170" windowWidth="21870" windowHeight="19545" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2295" yWindow="1170" windowWidth="21870" windowHeight="19545" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Útok" sheetId="1" r:id="rId1"/>
     <sheet name="Obrana" sheetId="2" r:id="rId2"/>
+    <sheet name="Útok (2)" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>attack_type</t>
   </si>
@@ -290,6 +291,18 @@
   </si>
   <si>
     <t xml:space="preserve">smrdíš </t>
+  </si>
+  <si>
+    <t>skill</t>
+  </si>
+  <si>
+    <t>lotr</t>
+  </si>
+  <si>
+    <t>bobr</t>
+  </si>
+  <si>
+    <t>makck</t>
   </si>
 </sst>
 </file>
@@ -1628,4 +1641,557 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A06CF681-9CE3-4003-8DEA-AA6C9951BB4B}">
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="6" width="12.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" t="s">
+        <v>87</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srb\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A97CEC-6689-483C-8787-1A2C3AC79423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0840522-712A-4956-BCF5-6280518B11A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2295" yWindow="1170" windowWidth="21870" windowHeight="19545" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Útok" sheetId="1" r:id="rId1"/>
     <sheet name="Obrana" sheetId="2" r:id="rId2"/>
-    <sheet name="Útok (2)" sheetId="3" r:id="rId3"/>
+    <sheet name="Skill" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srb\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F291594-3B36-4669-A191-EA2FE1EDDD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD413FD-62DD-491C-8D8D-64DC2CF42EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="1170" windowWidth="21870" windowHeight="19545" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2295" yWindow="1170" windowWidth="26760" windowHeight="19545" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Útok" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4216" uniqueCount="1964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4517" uniqueCount="2144">
   <si>
     <t>attack_type</t>
   </si>
@@ -5919,6 +5919,546 @@
   </si>
   <si>
     <t>Slova ztratí význam.</t>
+  </si>
+  <si>
+    <t>Sranda</t>
+  </si>
+  <si>
+    <t>Něco se pokazilo spíš trapně než nebezpečně.</t>
+  </si>
+  <si>
+    <t>Zabereš tak moc, že si natáhneš sval a musíš si ho promnout.</t>
+  </si>
+  <si>
+    <t>Vypadá to hrozivě, ale nejvíc tě bolí tvoje hrdost.</t>
+  </si>
+  <si>
+    <t>Nepřítel síly je gravitace.</t>
+  </si>
+  <si>
+    <t>Zakřičíš bojový pokřik a uklouzneš na vlastní slině.</t>
+  </si>
+  <si>
+    <t>Dopad je tvrdý hlavně pro tvoje ego.</t>
+  </si>
+  <si>
+    <t>Výstroj selhává.</t>
+  </si>
+  <si>
+    <t>Při zvedání praskne opasek a kalhoty začnou klouzat dolů.</t>
+  </si>
+  <si>
+    <t>Všichni si všimnou dřív než ty.</t>
+  </si>
+  <si>
+    <t>Síla bez kontroly.</t>
+  </si>
+  <si>
+    <t>Zabereš a v ruce ti zůstane jen kus toho, co jsi chtěl zvednout.</t>
+  </si>
+  <si>
+    <t>Zbytek zůstane na místě a vysmívá se ti.</t>
+  </si>
+  <si>
+    <t>Síla špatným směrem.</t>
+  </si>
+  <si>
+    <t>Zakopneš o něco, co jsi měl překonat silou.</t>
+  </si>
+  <si>
+    <t>Pád je rychlejší než rozběh.</t>
+  </si>
+  <si>
+    <t>Zbraň má vlastní názor.</t>
+  </si>
+  <si>
+    <t>Uhodíš se vlastní zbraní do holeně.</t>
+  </si>
+  <si>
+    <t>Není to hrdinský moment.</t>
+  </si>
+  <si>
+    <t>Tělo vydá zvuk.</t>
+  </si>
+  <si>
+    <t>Ozve se hlasité „křup“.</t>
+  </si>
+  <si>
+    <t>Naštěstí jen kloub… pravděpodobně.</t>
+  </si>
+  <si>
+    <t>Přepálený pohyb.</t>
+  </si>
+  <si>
+    <t>Zabereš tak, že si loktem dáš do žeber.</t>
+  </si>
+  <si>
+    <t>Na chvíli ztratíš dech i důstojnost.</t>
+  </si>
+  <si>
+    <t>Překážka byla níž, než sis myslel.</t>
+  </si>
+  <si>
+    <t>Narazíš hlavou do objektu, který jsi nečekal.</t>
+  </si>
+  <si>
+    <t>Síla tu nepomohla.</t>
+  </si>
+  <si>
+    <t>Vítězství s následky.</t>
+  </si>
+  <si>
+    <t>Objekt se pohne… ty padáš.</t>
+  </si>
+  <si>
+    <t>Vyhrál jsi, ale za cenu pádu.</t>
+  </si>
+  <si>
+    <t>Obratnost se urazila.</t>
+  </si>
+  <si>
+    <t>Uklouzneš na naprosto suché podlaze.</t>
+  </si>
+  <si>
+    <t>Nikdo nechápe jak, ale stalo se.</t>
+  </si>
+  <si>
+    <t>Stealth level: špatný.</t>
+  </si>
+  <si>
+    <t>Šlápneš na prdící polštářek.</t>
+  </si>
+  <si>
+    <t>Ticho je definitivně pryč.</t>
+  </si>
+  <si>
+    <t>Pohyb s vedlejšími efekty.</t>
+  </si>
+  <si>
+    <t>Při kotoulu ti vypadne výbava po okolí.</t>
+  </si>
+  <si>
+    <t>Teď ví všichni, co nosíš.</t>
+  </si>
+  <si>
+    <t>Tělo sabotuje samo sebe.</t>
+  </si>
+  <si>
+    <t>Zakopneš o vlastní nohu.</t>
+  </si>
+  <si>
+    <t>Nikdo to nedokáže vysvětlit.</t>
+  </si>
+  <si>
+    <t>Směr byl správný.</t>
+  </si>
+  <si>
+    <t>Cíl už ne.</t>
+  </si>
+  <si>
+    <t>Hodíš předmět perfektně… ale úplně jinam.</t>
+  </si>
+  <si>
+    <t>Výsledek je komický.</t>
+  </si>
+  <si>
+    <t>Alergie na ticho.</t>
+  </si>
+  <si>
+    <t>Pokusíš se o tichý pohyb, ale kýchnutí to zkazí.</t>
+  </si>
+  <si>
+    <t>Elegance mizí.</t>
+  </si>
+  <si>
+    <t>Plášť útočí.</t>
+  </si>
+  <si>
+    <t>Při dopadu se zamotáš do vlastního oblečení.</t>
+  </si>
+  <si>
+    <t>Gravitace vítězí.</t>
+  </si>
+  <si>
+    <t>Přesná otočka… do zdi.</t>
+  </si>
+  <si>
+    <t>Otočíš se elegantně a narazíš.</t>
+  </si>
+  <si>
+    <t>Elegance byla, cíl ne.</t>
+  </si>
+  <si>
+    <t>Prsty mají kluzký den.</t>
+  </si>
+  <si>
+    <t>Předmět ti vystřelí z ruky.</t>
+  </si>
+  <si>
+    <t>Nikdo neví kam.</t>
+  </si>
+  <si>
+    <t>Styl ano, místo ne.</t>
+  </si>
+  <si>
+    <t>Dopadneš efektně, ale úplně špatně.</t>
+  </si>
+  <si>
+    <t>Aplaus nikde.</t>
+  </si>
+  <si>
+    <t>Tělo si stěžuje.</t>
+  </si>
+  <si>
+    <t>Dojde ti dech rychleji, než bys čekal.</t>
+  </si>
+  <si>
+    <t>Zní to hůř, než to je.</t>
+  </si>
+  <si>
+    <t>Nečekaný rytmus.</t>
+  </si>
+  <si>
+    <t>Dostaneš škytavku v nejhorší chvíli.</t>
+  </si>
+  <si>
+    <t>Nedá se ignorovat.</t>
+  </si>
+  <si>
+    <t>Dýchací problém.</t>
+  </si>
+  <si>
+    <t>Polkneš špatně a začneš kašlat.</t>
+  </si>
+  <si>
+    <t>Vypadá to dramaticky.</t>
+  </si>
+  <si>
+    <t>Zabolí tě břicho tak, že se musíš narovnat.</t>
+  </si>
+  <si>
+    <t>Nic vážného, ale viditelné.</t>
+  </si>
+  <si>
+    <t>Klasika.</t>
+  </si>
+  <si>
+    <t>Zapíchne tě v boku.</t>
+  </si>
+  <si>
+    <t>Tělo ti připomene, že existuje.</t>
+  </si>
+  <si>
+    <t>Teplotní chaos.</t>
+  </si>
+  <si>
+    <t>Je ti horko, pak zima, pak obojí.</t>
+  </si>
+  <si>
+    <t>Tělo si nevybere.</t>
+  </si>
+  <si>
+    <t>Pauza bez domluvy.</t>
+  </si>
+  <si>
+    <t>Musíš si na chvíli opřít ruce o kolena.</t>
+  </si>
+  <si>
+    <t>Dýchání je priorita.</t>
+  </si>
+  <si>
+    <t>Zívací útok.</t>
+  </si>
+  <si>
+    <t>Zívneš tak silně, že si natáhneš čelist.</t>
+  </si>
+  <si>
+    <t>Nikdo to nečekal.</t>
+  </si>
+  <si>
+    <t>Organismus odmítá.</t>
+  </si>
+  <si>
+    <t>Tělo si prostě řekne „ne“.</t>
+  </si>
+  <si>
+    <t>Bez vysvětlení.</t>
+  </si>
+  <si>
+    <t>Zvuková signalizace.</t>
+  </si>
+  <si>
+    <t>Ozve se hlasité kručení žaludku.</t>
+  </si>
+  <si>
+    <t>Všichni slyší.</t>
+  </si>
+  <si>
+    <t>Logika funguje… špatně.</t>
+  </si>
+  <si>
+    <t>Vysvětlíš to skvěle, ale úplně blbě.</t>
+  </si>
+  <si>
+    <t>Dává to smysl jen tobě.</t>
+  </si>
+  <si>
+    <t>Výpadek slovníku.</t>
+  </si>
+  <si>
+    <t>Zapomeneš slovo uprostřed věty.</t>
+  </si>
+  <si>
+    <t>Věta končí trapně.</t>
+  </si>
+  <si>
+    <t>Geniální omyl.</t>
+  </si>
+  <si>
+    <t>Dojdeš k brilantnímu závěru z chybných dat.</t>
+  </si>
+  <si>
+    <t>Jsi na sebe hrdý… zatím.</t>
+  </si>
+  <si>
+    <t>Záměna pojmů.</t>
+  </si>
+  <si>
+    <t>Spleteš si dvě naprosto základní věci.</t>
+  </si>
+  <si>
+    <t>Nikdo neví, jestli vtipkuješ.</t>
+  </si>
+  <si>
+    <t>Pozdní uvědomění.</t>
+  </si>
+  <si>
+    <t>Chybu si uvědomíš až poté, co to řekneš nahlas.</t>
+  </si>
+  <si>
+    <t>Ticho je výmluvné.</t>
+  </si>
+  <si>
+    <t>Plán z jiného dne.</t>
+  </si>
+  <si>
+    <t>Vysvětlíš plán, který by fungoval… jindy.</t>
+  </si>
+  <si>
+    <t>Tady ne.</t>
+  </si>
+  <si>
+    <t>Jména jsou nepřátelé.</t>
+  </si>
+  <si>
+    <t>Popleteš si jména, pojmy nebo směry.</t>
+  </si>
+  <si>
+    <t>Někdo se urazí.</t>
+  </si>
+  <si>
+    <t>Falešné „aha“.</t>
+  </si>
+  <si>
+    <t>Řekneš „aha!“ bez toho, abys věděl proč.</t>
+  </si>
+  <si>
+    <t>Všichni čekají pokračování.</t>
+  </si>
+  <si>
+    <t>Chaotický výklad.</t>
+  </si>
+  <si>
+    <t>Vysvětlování se ti úplně zamotá.</t>
+  </si>
+  <si>
+    <t>Nikdo neví, kde začalo.</t>
+  </si>
+  <si>
+    <t>Vlastní realita.</t>
+  </si>
+  <si>
+    <t>Logika dává smysl jen v tvojí hlavě.</t>
+  </si>
+  <si>
+    <t>Ostatní tápu.</t>
+  </si>
+  <si>
+    <t>Slepé místo.</t>
+  </si>
+  <si>
+    <t>Koukáš přímo na to… a stejně to nevidíš.</t>
+  </si>
+  <si>
+    <t>Všichni ostatní ano.</t>
+  </si>
+  <si>
+    <t>Pohoda až moc.</t>
+  </si>
+  <si>
+    <t>Ignoruješ jasné varování.</t>
+  </si>
+  <si>
+    <t>„To je určitě v pohodě.“</t>
+  </si>
+  <si>
+    <t>Čtení místnosti selhalo.</t>
+  </si>
+  <si>
+    <t>Špatně odhadneš náladu úplně všech.</t>
+  </si>
+  <si>
+    <t>Ticho houstne.</t>
+  </si>
+  <si>
+    <t>Opačná reakce.</t>
+  </si>
+  <si>
+    <t>Zareaguješ přesně opačně, než by bylo vhodné.</t>
+  </si>
+  <si>
+    <t>Okolí nechápe.</t>
+  </si>
+  <si>
+    <t>Jsi jediný.</t>
+  </si>
+  <si>
+    <t>Všichni vidí hrozbu, jen ty ne.</t>
+  </si>
+  <si>
+    <t>Ani teď.</t>
+  </si>
+  <si>
+    <t>Pozdě.</t>
+  </si>
+  <si>
+    <t>Zareaguješ o jednu vteřinu pozdě.</t>
+  </si>
+  <si>
+    <t>Ale fakt jen o jednu.</t>
+  </si>
+  <si>
+    <t>Vnitřní hlas má dovolenou.</t>
+  </si>
+  <si>
+    <t>Rozhodnutí je náhodné.</t>
+  </si>
+  <si>
+    <t>Panika z ničeho.</t>
+  </si>
+  <si>
+    <t>Zbytečně se vyděsíš maličkostí.</t>
+  </si>
+  <si>
+    <t>Reakce je přehnaná.</t>
+  </si>
+  <si>
+    <t>Špatná důvěra.</t>
+  </si>
+  <si>
+    <t>Věříš přesně té nejhorší možnosti.</t>
+  </si>
+  <si>
+    <t>Ale upřímně.</t>
+  </si>
+  <si>
+    <t>Zpětné osvícení.</t>
+  </si>
+  <si>
+    <t>Až pozdě ti dojde, že to byl špatný nápad.</t>
+  </si>
+  <si>
+    <t>Hodně pozdě.</t>
+  </si>
+  <si>
+    <t>Forma zabije obsah.</t>
+  </si>
+  <si>
+    <t>Řekneš to správně, ale strašně trapně.</t>
+  </si>
+  <si>
+    <t>Dojem je nezvratný.</t>
+  </si>
+  <si>
+    <t>Vtip bez publika.</t>
+  </si>
+  <si>
+    <t>Vtip nedopadne.</t>
+  </si>
+  <si>
+    <t>Ticho bolí.</t>
+  </si>
+  <si>
+    <t>Jazyková past.</t>
+  </si>
+  <si>
+    <t>Zakoktáš se v klíčové větě.</t>
+  </si>
+  <si>
+    <t>Autorita mizí.</t>
+  </si>
+  <si>
+    <t>Nepovedená slova.</t>
+  </si>
+  <si>
+    <t>Řekneš něco, co zní jako urážka.</t>
+  </si>
+  <si>
+    <t>Nechtěně.</t>
+  </si>
+  <si>
+    <t>Snaha byla.</t>
+  </si>
+  <si>
+    <t>Snažíš se být cool.</t>
+  </si>
+  <si>
+    <t>Nejsi.</t>
+  </si>
+  <si>
+    <t>Titulární chyba.</t>
+  </si>
+  <si>
+    <t>Oslovíš špatnou osobu špatným titulem.</t>
+  </si>
+  <si>
+    <t>Oprava nepomůže.</t>
+  </si>
+  <si>
+    <t>Výpadek myšlenky.</t>
+  </si>
+  <si>
+    <t>Zapomeneš, co jsi chtěl říct.</t>
+  </si>
+  <si>
+    <t>Všichni čekají.</t>
+  </si>
+  <si>
+    <t>Tón mimo.</t>
+  </si>
+  <si>
+    <t>Tón hlasu vyzní úplně jinak, než jsi chtěl.</t>
+  </si>
+  <si>
+    <t>Reakce je rozpačitá.</t>
+  </si>
+  <si>
+    <t>Špatný úsměv.</t>
+  </si>
+  <si>
+    <t>Usměješ se v naprosto nevhodný moment.</t>
+  </si>
+  <si>
+    <t>Někdo si to zapamatuje.</t>
+  </si>
+  <si>
+    <t>Záchrana selhala.</t>
+  </si>
+  <si>
+    <t>Pokusíš se zachránit situaci… a ještě ji zhoršíš.</t>
+  </si>
+  <si>
+    <t>Teď je to osobní.</t>
   </si>
 </sst>
 </file>
@@ -6239,7 +6779,12 @@
   <dimension ref="A1:F282"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="72.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11892,7 +12437,11 @@
   <dimension ref="A1:E137"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="80.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -14231,10 +14780,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A06CF681-9CE3-4003-8DEA-AA6C9951BB4B}">
-  <dimension ref="A1:F451"/>
+  <dimension ref="A1:G511"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="72.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -23257,6 +23811,1209 @@
         <v>1</v>
       </c>
     </row>
+    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>818</v>
+      </c>
+      <c r="B452" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C452" t="s">
+        <v>1965</v>
+      </c>
+      <c r="D452" t="s">
+        <v>1966</v>
+      </c>
+      <c r="E452" t="s">
+        <v>1967</v>
+      </c>
+      <c r="F452">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>818</v>
+      </c>
+      <c r="B453" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C453" t="s">
+        <v>1968</v>
+      </c>
+      <c r="D453" t="s">
+        <v>1969</v>
+      </c>
+      <c r="E453" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F453">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>818</v>
+      </c>
+      <c r="B454" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C454" t="s">
+        <v>1971</v>
+      </c>
+      <c r="D454" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E454" t="s">
+        <v>1973</v>
+      </c>
+      <c r="F454">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>818</v>
+      </c>
+      <c r="B455" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C455" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D455" t="s">
+        <v>1975</v>
+      </c>
+      <c r="E455" t="s">
+        <v>1976</v>
+      </c>
+      <c r="F455">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>818</v>
+      </c>
+      <c r="B456" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C456" t="s">
+        <v>1977</v>
+      </c>
+      <c r="D456" t="s">
+        <v>1978</v>
+      </c>
+      <c r="E456" t="s">
+        <v>1979</v>
+      </c>
+      <c r="F456">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>818</v>
+      </c>
+      <c r="B457" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C457" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D457" t="s">
+        <v>1981</v>
+      </c>
+      <c r="E457" t="s">
+        <v>1982</v>
+      </c>
+      <c r="F457">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>818</v>
+      </c>
+      <c r="B458" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C458" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D458" t="s">
+        <v>1984</v>
+      </c>
+      <c r="E458" t="s">
+        <v>1985</v>
+      </c>
+      <c r="F458">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>818</v>
+      </c>
+      <c r="B459" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C459" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D459" t="s">
+        <v>1987</v>
+      </c>
+      <c r="E459" t="s">
+        <v>1988</v>
+      </c>
+      <c r="F459">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>818</v>
+      </c>
+      <c r="B460" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C460" t="s">
+        <v>1989</v>
+      </c>
+      <c r="D460" t="s">
+        <v>1990</v>
+      </c>
+      <c r="E460" t="s">
+        <v>1991</v>
+      </c>
+      <c r="F460">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>818</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C461" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D461" t="s">
+        <v>1993</v>
+      </c>
+      <c r="E461" t="s">
+        <v>1994</v>
+      </c>
+      <c r="F461">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C462" t="s">
+        <v>1995</v>
+      </c>
+      <c r="D462" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E462" t="s">
+        <v>1997</v>
+      </c>
+      <c r="F462">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B463" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C463" t="s">
+        <v>1998</v>
+      </c>
+      <c r="D463" t="s">
+        <v>1999</v>
+      </c>
+      <c r="E463" t="s">
+        <v>2000</v>
+      </c>
+      <c r="F463">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B464" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C464" t="s">
+        <v>2001</v>
+      </c>
+      <c r="D464" t="s">
+        <v>2002</v>
+      </c>
+      <c r="E464" t="s">
+        <v>2003</v>
+      </c>
+      <c r="F464">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B465" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C465" t="s">
+        <v>2004</v>
+      </c>
+      <c r="D465" t="s">
+        <v>2005</v>
+      </c>
+      <c r="E465" t="s">
+        <v>2006</v>
+      </c>
+      <c r="F465">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C466" t="s">
+        <v>2007</v>
+      </c>
+      <c r="D466" t="s">
+        <v>2008</v>
+      </c>
+      <c r="E466" t="s">
+        <v>2009</v>
+      </c>
+      <c r="F466" t="s">
+        <v>2010</v>
+      </c>
+      <c r="G466">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C467" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D467" t="s">
+        <v>2012</v>
+      </c>
+      <c r="E467" t="s">
+        <v>2013</v>
+      </c>
+      <c r="F467">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C468" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D468" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E468" t="s">
+        <v>2016</v>
+      </c>
+      <c r="F468">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C469" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D469" t="s">
+        <v>2018</v>
+      </c>
+      <c r="E469" t="s">
+        <v>2019</v>
+      </c>
+      <c r="F469">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C470" t="s">
+        <v>2020</v>
+      </c>
+      <c r="D470" t="s">
+        <v>2021</v>
+      </c>
+      <c r="E470" t="s">
+        <v>2022</v>
+      </c>
+      <c r="F470">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C471" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D471" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E471" t="s">
+        <v>2025</v>
+      </c>
+      <c r="F471">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C472" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D472" t="s">
+        <v>2027</v>
+      </c>
+      <c r="E472" t="s">
+        <v>2028</v>
+      </c>
+      <c r="F472">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C473" t="s">
+        <v>2029</v>
+      </c>
+      <c r="D473" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E473" t="s">
+        <v>2031</v>
+      </c>
+      <c r="F473">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C474" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D474" t="s">
+        <v>2033</v>
+      </c>
+      <c r="E474" t="s">
+        <v>2034</v>
+      </c>
+      <c r="F474">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C475" t="s">
+        <v>963</v>
+      </c>
+      <c r="D475" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E475" t="s">
+        <v>2036</v>
+      </c>
+      <c r="F475">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C476" t="s">
+        <v>2037</v>
+      </c>
+      <c r="D476" t="s">
+        <v>2038</v>
+      </c>
+      <c r="E476" t="s">
+        <v>2039</v>
+      </c>
+      <c r="F476">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C477" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D477" t="s">
+        <v>2041</v>
+      </c>
+      <c r="E477" t="s">
+        <v>2042</v>
+      </c>
+      <c r="F477">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C478" t="s">
+        <v>2043</v>
+      </c>
+      <c r="D478" t="s">
+        <v>2044</v>
+      </c>
+      <c r="E478" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F478">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B479" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C479" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D479" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E479" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F479">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C480" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D480" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E480" t="s">
+        <v>2051</v>
+      </c>
+      <c r="F480">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C481" t="s">
+        <v>2052</v>
+      </c>
+      <c r="D481" t="s">
+        <v>2053</v>
+      </c>
+      <c r="E481" t="s">
+        <v>2054</v>
+      </c>
+      <c r="F481">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C482" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D482" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E482" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F482">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C483" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D483" t="s">
+        <v>2059</v>
+      </c>
+      <c r="E483" t="s">
+        <v>2060</v>
+      </c>
+      <c r="F483">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C484" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D484" t="s">
+        <v>2062</v>
+      </c>
+      <c r="E484" t="s">
+        <v>2063</v>
+      </c>
+      <c r="F484">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C485" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D485" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E485" t="s">
+        <v>2066</v>
+      </c>
+      <c r="F485">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B486" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C486" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D486" t="s">
+        <v>2068</v>
+      </c>
+      <c r="E486" t="s">
+        <v>2069</v>
+      </c>
+      <c r="F486">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B487" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C487" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D487" t="s">
+        <v>2071</v>
+      </c>
+      <c r="E487" t="s">
+        <v>2072</v>
+      </c>
+      <c r="F487">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C488" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D488" t="s">
+        <v>2074</v>
+      </c>
+      <c r="E488" t="s">
+        <v>2075</v>
+      </c>
+      <c r="F488">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C489" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D489" t="s">
+        <v>2077</v>
+      </c>
+      <c r="E489" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F489">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C490" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D490" t="s">
+        <v>2080</v>
+      </c>
+      <c r="E490" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F490">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B491" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C491" t="s">
+        <v>2082</v>
+      </c>
+      <c r="D491" t="s">
+        <v>2083</v>
+      </c>
+      <c r="E491" t="s">
+        <v>2084</v>
+      </c>
+      <c r="F491">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B492" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C492" t="s">
+        <v>2085</v>
+      </c>
+      <c r="D492" t="s">
+        <v>2086</v>
+      </c>
+      <c r="E492" t="s">
+        <v>2087</v>
+      </c>
+      <c r="F492">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="493" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B493" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C493" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D493" t="s">
+        <v>2089</v>
+      </c>
+      <c r="E493" t="s">
+        <v>2090</v>
+      </c>
+      <c r="F493">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B494" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C494" t="s">
+        <v>2091</v>
+      </c>
+      <c r="D494" t="s">
+        <v>2092</v>
+      </c>
+      <c r="E494" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F494">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B495" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C495" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D495" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E495" t="s">
+        <v>2096</v>
+      </c>
+      <c r="F495">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C496" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D496" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E496" t="s">
+        <v>2099</v>
+      </c>
+      <c r="F496">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C497" t="s">
+        <v>2100</v>
+      </c>
+      <c r="D497" t="s">
+        <v>2101</v>
+      </c>
+      <c r="E497" t="s">
+        <v>2102</v>
+      </c>
+      <c r="F497">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C498" t="s">
+        <v>2103</v>
+      </c>
+      <c r="D498" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E498" t="s">
+        <v>2104</v>
+      </c>
+      <c r="F498">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C499" t="s">
+        <v>2105</v>
+      </c>
+      <c r="D499" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E499" t="s">
+        <v>2107</v>
+      </c>
+      <c r="F499">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C500" t="s">
+        <v>2108</v>
+      </c>
+      <c r="D500" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E500" t="s">
+        <v>2110</v>
+      </c>
+      <c r="F500">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C501" t="s">
+        <v>2111</v>
+      </c>
+      <c r="D501" t="s">
+        <v>2112</v>
+      </c>
+      <c r="E501" t="s">
+        <v>2113</v>
+      </c>
+      <c r="F501">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C502" t="s">
+        <v>2114</v>
+      </c>
+      <c r="D502" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E502" t="s">
+        <v>2116</v>
+      </c>
+      <c r="F502">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C503" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D503" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E503" t="s">
+        <v>2119</v>
+      </c>
+      <c r="F503">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C504" t="s">
+        <v>2120</v>
+      </c>
+      <c r="D504" t="s">
+        <v>2121</v>
+      </c>
+      <c r="E504" t="s">
+        <v>2122</v>
+      </c>
+      <c r="F504">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C505" t="s">
+        <v>2123</v>
+      </c>
+      <c r="D505" t="s">
+        <v>2124</v>
+      </c>
+      <c r="E505" t="s">
+        <v>2125</v>
+      </c>
+      <c r="F505">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C506" t="s">
+        <v>2126</v>
+      </c>
+      <c r="D506" t="s">
+        <v>2127</v>
+      </c>
+      <c r="E506" t="s">
+        <v>2128</v>
+      </c>
+      <c r="F506">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C507" t="s">
+        <v>2129</v>
+      </c>
+      <c r="D507" t="s">
+        <v>2130</v>
+      </c>
+      <c r="E507" t="s">
+        <v>2131</v>
+      </c>
+      <c r="F507">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C508" t="s">
+        <v>2132</v>
+      </c>
+      <c r="D508" t="s">
+        <v>2133</v>
+      </c>
+      <c r="E508" t="s">
+        <v>2134</v>
+      </c>
+      <c r="F508">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C509" t="s">
+        <v>2135</v>
+      </c>
+      <c r="D509" t="s">
+        <v>2136</v>
+      </c>
+      <c r="E509" t="s">
+        <v>2137</v>
+      </c>
+      <c r="F509">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C510" t="s">
+        <v>2138</v>
+      </c>
+      <c r="D510" t="s">
+        <v>2139</v>
+      </c>
+      <c r="E510" t="s">
+        <v>2140</v>
+      </c>
+      <c r="F510">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1964</v>
+      </c>
+      <c r="C511" t="s">
+        <v>2141</v>
+      </c>
+      <c r="D511" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E511" t="s">
+        <v>2143</v>
+      </c>
+      <c r="F511">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srb\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD413FD-62DD-491C-8D8D-64DC2CF42EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5B0E23-1F95-4CC2-8F21-8CBD7C178C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2295" yWindow="1170" windowWidth="26760" windowHeight="19545" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4517" uniqueCount="2144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4516" uniqueCount="2143">
   <si>
     <t>attack_type</t>
   </si>
@@ -6057,9 +6057,6 @@
   </si>
   <si>
     <t>Hodíš předmět perfektně… ale úplně jinam.</t>
-  </si>
-  <si>
-    <t>Výsledek je komický.</t>
   </si>
   <si>
     <t>Alergie na ticho.</t>
@@ -14780,7 +14777,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A06CF681-9CE3-4003-8DEA-AA6C9951BB4B}">
-  <dimension ref="A1:G511"/>
+  <dimension ref="A1:F511"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -24071,7 +24068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>1038</v>
       </c>
@@ -24091,7 +24088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>1038</v>
       </c>
@@ -24107,14 +24104,11 @@
       <c r="E466" t="s">
         <v>2009</v>
       </c>
-      <c r="F466" t="s">
-        <v>2010</v>
-      </c>
-      <c r="G466">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F466">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>1038</v>
       </c>
@@ -24122,19 +24116,19 @@
         <v>1964</v>
       </c>
       <c r="C467" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D467" t="s">
         <v>2011</v>
       </c>
-      <c r="D467" t="s">
+      <c r="E467" t="s">
         <v>2012</v>
       </c>
-      <c r="E467" t="s">
-        <v>2013</v>
-      </c>
       <c r="F467">
         <v>1</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>1038</v>
       </c>
@@ -24142,19 +24136,19 @@
         <v>1964</v>
       </c>
       <c r="C468" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D468" t="s">
         <v>2014</v>
       </c>
-      <c r="D468" t="s">
+      <c r="E468" t="s">
         <v>2015</v>
       </c>
-      <c r="E468" t="s">
-        <v>2016</v>
-      </c>
       <c r="F468">
         <v>1</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>1038</v>
       </c>
@@ -24162,19 +24156,19 @@
         <v>1964</v>
       </c>
       <c r="C469" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D469" t="s">
         <v>2017</v>
       </c>
-      <c r="D469" t="s">
+      <c r="E469" t="s">
         <v>2018</v>
       </c>
-      <c r="E469" t="s">
-        <v>2019</v>
-      </c>
       <c r="F469">
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>1038</v>
       </c>
@@ -24182,19 +24176,19 @@
         <v>1964</v>
       </c>
       <c r="C470" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D470" t="s">
         <v>2020</v>
       </c>
-      <c r="D470" t="s">
+      <c r="E470" t="s">
         <v>2021</v>
       </c>
-      <c r="E470" t="s">
-        <v>2022</v>
-      </c>
       <c r="F470">
         <v>1</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>1038</v>
       </c>
@@ -24202,19 +24196,19 @@
         <v>1964</v>
       </c>
       <c r="C471" t="s">
+        <v>2022</v>
+      </c>
+      <c r="D471" t="s">
         <v>2023</v>
       </c>
-      <c r="D471" t="s">
+      <c r="E471" t="s">
         <v>2024</v>
       </c>
-      <c r="E471" t="s">
-        <v>2025</v>
-      </c>
       <c r="F471">
         <v>1</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>1232</v>
       </c>
@@ -24222,19 +24216,19 @@
         <v>1964</v>
       </c>
       <c r="C472" t="s">
+        <v>2025</v>
+      </c>
+      <c r="D472" t="s">
         <v>2026</v>
       </c>
-      <c r="D472" t="s">
+      <c r="E472" t="s">
         <v>2027</v>
       </c>
-      <c r="E472" t="s">
-        <v>2028</v>
-      </c>
       <c r="F472">
         <v>1</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>1232</v>
       </c>
@@ -24242,19 +24236,19 @@
         <v>1964</v>
       </c>
       <c r="C473" t="s">
+        <v>2028</v>
+      </c>
+      <c r="D473" t="s">
         <v>2029</v>
       </c>
-      <c r="D473" t="s">
+      <c r="E473" t="s">
         <v>2030</v>
       </c>
-      <c r="E473" t="s">
-        <v>2031</v>
-      </c>
       <c r="F473">
         <v>1</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>1232</v>
       </c>
@@ -24262,19 +24256,19 @@
         <v>1964</v>
       </c>
       <c r="C474" t="s">
+        <v>2031</v>
+      </c>
+      <c r="D474" t="s">
         <v>2032</v>
       </c>
-      <c r="D474" t="s">
+      <c r="E474" t="s">
         <v>2033</v>
       </c>
-      <c r="E474" t="s">
-        <v>2034</v>
-      </c>
       <c r="F474">
         <v>1</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>1232</v>
       </c>
@@ -24285,16 +24279,16 @@
         <v>963</v>
       </c>
       <c r="D475" t="s">
+        <v>2034</v>
+      </c>
+      <c r="E475" t="s">
         <v>2035</v>
       </c>
-      <c r="E475" t="s">
-        <v>2036</v>
-      </c>
       <c r="F475">
         <v>1</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>1232</v>
       </c>
@@ -24302,19 +24296,19 @@
         <v>1964</v>
       </c>
       <c r="C476" t="s">
+        <v>2036</v>
+      </c>
+      <c r="D476" t="s">
         <v>2037</v>
       </c>
-      <c r="D476" t="s">
+      <c r="E476" t="s">
         <v>2038</v>
       </c>
-      <c r="E476" t="s">
-        <v>2039</v>
-      </c>
       <c r="F476">
         <v>1</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>1232</v>
       </c>
@@ -24322,19 +24316,19 @@
         <v>1964</v>
       </c>
       <c r="C477" t="s">
+        <v>2039</v>
+      </c>
+      <c r="D477" t="s">
         <v>2040</v>
       </c>
-      <c r="D477" t="s">
+      <c r="E477" t="s">
         <v>2041</v>
       </c>
-      <c r="E477" t="s">
-        <v>2042</v>
-      </c>
       <c r="F477">
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>1232</v>
       </c>
@@ -24342,19 +24336,19 @@
         <v>1964</v>
       </c>
       <c r="C478" t="s">
+        <v>2042</v>
+      </c>
+      <c r="D478" t="s">
         <v>2043</v>
       </c>
-      <c r="D478" t="s">
+      <c r="E478" t="s">
         <v>2044</v>
       </c>
-      <c r="E478" t="s">
-        <v>2045</v>
-      </c>
       <c r="F478">
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>1232</v>
       </c>
@@ -24362,19 +24356,19 @@
         <v>1964</v>
       </c>
       <c r="C479" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D479" t="s">
         <v>2046</v>
       </c>
-      <c r="D479" t="s">
+      <c r="E479" t="s">
         <v>2047</v>
       </c>
-      <c r="E479" t="s">
-        <v>2048</v>
-      </c>
       <c r="F479">
         <v>1</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>1232</v>
       </c>
@@ -24382,13 +24376,13 @@
         <v>1964</v>
       </c>
       <c r="C480" t="s">
+        <v>2048</v>
+      </c>
+      <c r="D480" t="s">
         <v>2049</v>
       </c>
-      <c r="D480" t="s">
+      <c r="E480" t="s">
         <v>2050</v>
-      </c>
-      <c r="E480" t="s">
-        <v>2051</v>
       </c>
       <c r="F480">
         <v>1</v>
@@ -24402,13 +24396,13 @@
         <v>1964</v>
       </c>
       <c r="C481" t="s">
+        <v>2051</v>
+      </c>
+      <c r="D481" t="s">
         <v>2052</v>
       </c>
-      <c r="D481" t="s">
+      <c r="E481" t="s">
         <v>2053</v>
-      </c>
-      <c r="E481" t="s">
-        <v>2054</v>
       </c>
       <c r="F481">
         <v>1</v>
@@ -24422,13 +24416,13 @@
         <v>1964</v>
       </c>
       <c r="C482" t="s">
+        <v>2054</v>
+      </c>
+      <c r="D482" t="s">
         <v>2055</v>
       </c>
-      <c r="D482" t="s">
+      <c r="E482" t="s">
         <v>2056</v>
-      </c>
-      <c r="E482" t="s">
-        <v>2057</v>
       </c>
       <c r="F482">
         <v>1</v>
@@ -24442,13 +24436,13 @@
         <v>1964</v>
       </c>
       <c r="C483" t="s">
+        <v>2057</v>
+      </c>
+      <c r="D483" t="s">
         <v>2058</v>
       </c>
-      <c r="D483" t="s">
+      <c r="E483" t="s">
         <v>2059</v>
-      </c>
-      <c r="E483" t="s">
-        <v>2060</v>
       </c>
       <c r="F483">
         <v>1</v>
@@ -24462,13 +24456,13 @@
         <v>1964</v>
       </c>
       <c r="C484" t="s">
+        <v>2060</v>
+      </c>
+      <c r="D484" t="s">
         <v>2061</v>
       </c>
-      <c r="D484" t="s">
+      <c r="E484" t="s">
         <v>2062</v>
-      </c>
-      <c r="E484" t="s">
-        <v>2063</v>
       </c>
       <c r="F484">
         <v>1</v>
@@ -24482,13 +24476,13 @@
         <v>1964</v>
       </c>
       <c r="C485" t="s">
+        <v>2063</v>
+      </c>
+      <c r="D485" t="s">
         <v>2064</v>
       </c>
-      <c r="D485" t="s">
+      <c r="E485" t="s">
         <v>2065</v>
-      </c>
-      <c r="E485" t="s">
-        <v>2066</v>
       </c>
       <c r="F485">
         <v>1</v>
@@ -24502,13 +24496,13 @@
         <v>1964</v>
       </c>
       <c r="C486" t="s">
+        <v>2066</v>
+      </c>
+      <c r="D486" t="s">
         <v>2067</v>
       </c>
-      <c r="D486" t="s">
+      <c r="E486" t="s">
         <v>2068</v>
-      </c>
-      <c r="E486" t="s">
-        <v>2069</v>
       </c>
       <c r="F486">
         <v>1</v>
@@ -24522,13 +24516,13 @@
         <v>1964</v>
       </c>
       <c r="C487" t="s">
+        <v>2069</v>
+      </c>
+      <c r="D487" t="s">
         <v>2070</v>
       </c>
-      <c r="D487" t="s">
+      <c r="E487" t="s">
         <v>2071</v>
-      </c>
-      <c r="E487" t="s">
-        <v>2072</v>
       </c>
       <c r="F487">
         <v>1</v>
@@ -24542,13 +24536,13 @@
         <v>1964</v>
       </c>
       <c r="C488" t="s">
+        <v>2072</v>
+      </c>
+      <c r="D488" t="s">
         <v>2073</v>
       </c>
-      <c r="D488" t="s">
+      <c r="E488" t="s">
         <v>2074</v>
-      </c>
-      <c r="E488" t="s">
-        <v>2075</v>
       </c>
       <c r="F488">
         <v>1</v>
@@ -24562,13 +24556,13 @@
         <v>1964</v>
       </c>
       <c r="C489" t="s">
+        <v>2075</v>
+      </c>
+      <c r="D489" t="s">
         <v>2076</v>
       </c>
-      <c r="D489" t="s">
+      <c r="E489" t="s">
         <v>2077</v>
-      </c>
-      <c r="E489" t="s">
-        <v>2078</v>
       </c>
       <c r="F489">
         <v>1</v>
@@ -24582,13 +24576,13 @@
         <v>1964</v>
       </c>
       <c r="C490" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D490" t="s">
         <v>2079</v>
       </c>
-      <c r="D490" t="s">
+      <c r="E490" t="s">
         <v>2080</v>
-      </c>
-      <c r="E490" t="s">
-        <v>2081</v>
       </c>
       <c r="F490">
         <v>1</v>
@@ -24602,13 +24596,13 @@
         <v>1964</v>
       </c>
       <c r="C491" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D491" t="s">
         <v>2082</v>
       </c>
-      <c r="D491" t="s">
+      <c r="E491" t="s">
         <v>2083</v>
-      </c>
-      <c r="E491" t="s">
-        <v>2084</v>
       </c>
       <c r="F491">
         <v>1</v>
@@ -24622,13 +24616,13 @@
         <v>1964</v>
       </c>
       <c r="C492" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D492" t="s">
         <v>2085</v>
       </c>
-      <c r="D492" t="s">
+      <c r="E492" t="s">
         <v>2086</v>
-      </c>
-      <c r="E492" t="s">
-        <v>2087</v>
       </c>
       <c r="F492">
         <v>1</v>
@@ -24642,13 +24636,13 @@
         <v>1964</v>
       </c>
       <c r="C493" t="s">
+        <v>2087</v>
+      </c>
+      <c r="D493" t="s">
         <v>2088</v>
       </c>
-      <c r="D493" t="s">
+      <c r="E493" t="s">
         <v>2089</v>
-      </c>
-      <c r="E493" t="s">
-        <v>2090</v>
       </c>
       <c r="F493">
         <v>1</v>
@@ -24662,13 +24656,13 @@
         <v>1964</v>
       </c>
       <c r="C494" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D494" t="s">
         <v>2091</v>
       </c>
-      <c r="D494" t="s">
+      <c r="E494" t="s">
         <v>2092</v>
-      </c>
-      <c r="E494" t="s">
-        <v>2093</v>
       </c>
       <c r="F494">
         <v>1</v>
@@ -24682,13 +24676,13 @@
         <v>1964</v>
       </c>
       <c r="C495" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D495" t="s">
         <v>2094</v>
       </c>
-      <c r="D495" t="s">
+      <c r="E495" t="s">
         <v>2095</v>
-      </c>
-      <c r="E495" t="s">
-        <v>2096</v>
       </c>
       <c r="F495">
         <v>1</v>
@@ -24702,13 +24696,13 @@
         <v>1964</v>
       </c>
       <c r="C496" t="s">
+        <v>2096</v>
+      </c>
+      <c r="D496" t="s">
         <v>2097</v>
       </c>
-      <c r="D496" t="s">
+      <c r="E496" t="s">
         <v>2098</v>
-      </c>
-      <c r="E496" t="s">
-        <v>2099</v>
       </c>
       <c r="F496">
         <v>1</v>
@@ -24722,13 +24716,13 @@
         <v>1964</v>
       </c>
       <c r="C497" t="s">
+        <v>2099</v>
+      </c>
+      <c r="D497" t="s">
         <v>2100</v>
       </c>
-      <c r="D497" t="s">
+      <c r="E497" t="s">
         <v>2101</v>
-      </c>
-      <c r="E497" t="s">
-        <v>2102</v>
       </c>
       <c r="F497">
         <v>1</v>
@@ -24742,13 +24736,13 @@
         <v>1964</v>
       </c>
       <c r="C498" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="D498" t="s">
         <v>1667</v>
       </c>
       <c r="E498" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="F498">
         <v>1</v>
@@ -24762,13 +24756,13 @@
         <v>1964</v>
       </c>
       <c r="C499" t="s">
+        <v>2104</v>
+      </c>
+      <c r="D499" t="s">
         <v>2105</v>
       </c>
-      <c r="D499" t="s">
+      <c r="E499" t="s">
         <v>2106</v>
-      </c>
-      <c r="E499" t="s">
-        <v>2107</v>
       </c>
       <c r="F499">
         <v>1</v>
@@ -24782,13 +24776,13 @@
         <v>1964</v>
       </c>
       <c r="C500" t="s">
+        <v>2107</v>
+      </c>
+      <c r="D500" t="s">
         <v>2108</v>
       </c>
-      <c r="D500" t="s">
+      <c r="E500" t="s">
         <v>2109</v>
-      </c>
-      <c r="E500" t="s">
-        <v>2110</v>
       </c>
       <c r="F500">
         <v>1</v>
@@ -24802,13 +24796,13 @@
         <v>1964</v>
       </c>
       <c r="C501" t="s">
+        <v>2110</v>
+      </c>
+      <c r="D501" t="s">
         <v>2111</v>
       </c>
-      <c r="D501" t="s">
+      <c r="E501" t="s">
         <v>2112</v>
-      </c>
-      <c r="E501" t="s">
-        <v>2113</v>
       </c>
       <c r="F501">
         <v>1</v>
@@ -24822,13 +24816,13 @@
         <v>1964</v>
       </c>
       <c r="C502" t="s">
+        <v>2113</v>
+      </c>
+      <c r="D502" t="s">
         <v>2114</v>
       </c>
-      <c r="D502" t="s">
+      <c r="E502" t="s">
         <v>2115</v>
-      </c>
-      <c r="E502" t="s">
-        <v>2116</v>
       </c>
       <c r="F502">
         <v>1</v>
@@ -24842,13 +24836,13 @@
         <v>1964</v>
       </c>
       <c r="C503" t="s">
+        <v>2116</v>
+      </c>
+      <c r="D503" t="s">
         <v>2117</v>
       </c>
-      <c r="D503" t="s">
+      <c r="E503" t="s">
         <v>2118</v>
-      </c>
-      <c r="E503" t="s">
-        <v>2119</v>
       </c>
       <c r="F503">
         <v>1</v>
@@ -24862,13 +24856,13 @@
         <v>1964</v>
       </c>
       <c r="C504" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D504" t="s">
         <v>2120</v>
       </c>
-      <c r="D504" t="s">
+      <c r="E504" t="s">
         <v>2121</v>
-      </c>
-      <c r="E504" t="s">
-        <v>2122</v>
       </c>
       <c r="F504">
         <v>1</v>
@@ -24882,13 +24876,13 @@
         <v>1964</v>
       </c>
       <c r="C505" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D505" t="s">
         <v>2123</v>
       </c>
-      <c r="D505" t="s">
+      <c r="E505" t="s">
         <v>2124</v>
-      </c>
-      <c r="E505" t="s">
-        <v>2125</v>
       </c>
       <c r="F505">
         <v>1</v>
@@ -24902,13 +24896,13 @@
         <v>1964</v>
       </c>
       <c r="C506" t="s">
+        <v>2125</v>
+      </c>
+      <c r="D506" t="s">
         <v>2126</v>
       </c>
-      <c r="D506" t="s">
+      <c r="E506" t="s">
         <v>2127</v>
-      </c>
-      <c r="E506" t="s">
-        <v>2128</v>
       </c>
       <c r="F506">
         <v>1</v>
@@ -24922,13 +24916,13 @@
         <v>1964</v>
       </c>
       <c r="C507" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D507" t="s">
         <v>2129</v>
       </c>
-      <c r="D507" t="s">
+      <c r="E507" t="s">
         <v>2130</v>
-      </c>
-      <c r="E507" t="s">
-        <v>2131</v>
       </c>
       <c r="F507">
         <v>1</v>
@@ -24942,13 +24936,13 @@
         <v>1964</v>
       </c>
       <c r="C508" t="s">
+        <v>2131</v>
+      </c>
+      <c r="D508" t="s">
         <v>2132</v>
       </c>
-      <c r="D508" t="s">
+      <c r="E508" t="s">
         <v>2133</v>
-      </c>
-      <c r="E508" t="s">
-        <v>2134</v>
       </c>
       <c r="F508">
         <v>1</v>
@@ -24962,13 +24956,13 @@
         <v>1964</v>
       </c>
       <c r="C509" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D509" t="s">
         <v>2135</v>
       </c>
-      <c r="D509" t="s">
+      <c r="E509" t="s">
         <v>2136</v>
-      </c>
-      <c r="E509" t="s">
-        <v>2137</v>
       </c>
       <c r="F509">
         <v>1</v>
@@ -24982,13 +24976,13 @@
         <v>1964</v>
       </c>
       <c r="C510" t="s">
+        <v>2137</v>
+      </c>
+      <c r="D510" t="s">
         <v>2138</v>
       </c>
-      <c r="D510" t="s">
+      <c r="E510" t="s">
         <v>2139</v>
-      </c>
-      <c r="E510" t="s">
-        <v>2140</v>
       </c>
       <c r="F510">
         <v>1</v>
@@ -25002,13 +24996,13 @@
         <v>1964</v>
       </c>
       <c r="C511" t="s">
+        <v>2140</v>
+      </c>
+      <c r="D511" t="s">
         <v>2141</v>
       </c>
-      <c r="D511" t="s">
+      <c r="E511" t="s">
         <v>2142</v>
-      </c>
-      <c r="E511" t="s">
-        <v>2143</v>
       </c>
       <c r="F511">
         <v>1</v>

--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF12D1D7-0B1A-448C-9B94-C211EE128515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11190" yWindow="1140" windowWidth="33465" windowHeight="19545" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="2055" windowWidth="33465" windowHeight="19545" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Útok" sheetId="1" r:id="rId1"/>

--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srb\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF12D1D7-0B1A-448C-9B94-C211EE128515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92815BF9-ADCD-40CC-9351-C85E6DC067A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="2055" windowWidth="33465" windowHeight="19545" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="33465" windowHeight="19545" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Útok" sheetId="1" r:id="rId1"/>
@@ -16551,6 +16551,7 @@
     <col min="5" max="5" width="41.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">

--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71179D7E-A50A-432C-A3B8-E6A333139356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="2055" windowWidth="33465" windowHeight="19545" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="2055" windowWidth="33465" windowHeight="19545" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Útok" sheetId="1" r:id="rId1"/>

--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srb\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71179D7E-A50A-432C-A3B8-E6A333139356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D425A19-1F24-42A1-8ECC-78F06BC7AD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5070" yWindow="2055" windowWidth="33465" windowHeight="19545" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="33465" windowHeight="19545" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Útok" sheetId="1" r:id="rId1"/>
@@ -16551,7 +16551,8 @@
     <col min="5" max="5" width="41.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">

--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srb\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D425A19-1F24-42A1-8ECC-78F06BC7AD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FC562B-8E75-4C34-81DE-BD03BDA851A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="33465" windowHeight="19545" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4155" yWindow="885" windowWidth="23055" windowHeight="19545" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Útok" sheetId="1" r:id="rId1"/>
@@ -14203,6 +14203,7 @@
     <col min="3" max="3" width="39.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">

--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srb\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C50B4D-B437-46CC-8428-93BCBC9C43F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DAF8A85-09C3-4F9A-931E-FBC4895B6EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12285" yWindow="1170" windowWidth="33465" windowHeight="19545" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="33465" windowHeight="19545" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Útok" sheetId="1" r:id="rId1"/>
@@ -14207,6 +14207,7 @@
     <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
     <col min="13" max="13" width="11.85546875" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">

--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srb\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DAF8A85-09C3-4F9A-931E-FBC4895B6EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A630CA-7226-47C6-B24A-1B8A9EFA1B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="33465" windowHeight="19545" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10601" uniqueCount="2731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11301" uniqueCount="3087">
   <si>
     <t>attack_type</t>
   </si>
@@ -8220,6 +8220,1074 @@
   </si>
   <si>
     <t>Všechno bolí.</t>
+  </si>
+  <si>
+    <t>Švihneš a nohy tě zradí.</t>
+  </si>
+  <si>
+    <t>Na chvíli bojuješ spíš se zemí než s nepřítelem.</t>
+  </si>
+  <si>
+    <t>Upustíš zbraň.</t>
+  </si>
+  <si>
+    <t>Zbraň ti vyklouzne z ruky.</t>
+  </si>
+  <si>
+    <t>Kov cinkne o zem s trapným zvukem.</t>
+  </si>
+  <si>
+    <t>Otočíš se dokola.</t>
+  </si>
+  <si>
+    <t>Přehnaný švih tě roztočí.</t>
+  </si>
+  <si>
+    <t>Na moment nevíš, kde je nepřítel.</t>
+  </si>
+  <si>
+    <t>Zasekneš se v pozici.</t>
+  </si>
+  <si>
+    <t>Zůstaneš v divné póze.</t>
+  </si>
+  <si>
+    <t>Vypadáš jako socha bojovníka.</t>
+  </si>
+  <si>
+    <t>Uhodíš do vzduchu.</t>
+  </si>
+  <si>
+    <t>Švihneš úplně mimo.</t>
+  </si>
+  <si>
+    <t>Vzduch tě ale rozhodně neporazil.</t>
+  </si>
+  <si>
+    <t>Uděláš dramatický výkřik.</t>
+  </si>
+  <si>
+    <t>Křičíš víc než bojuješ.</t>
+  </si>
+  <si>
+    <t>Soupeř tě sleduje pobaveně.</t>
+  </si>
+  <si>
+    <t>Šlápneš na plášť.</t>
+  </si>
+  <si>
+    <t>Noha se ti zachytí do látky.</t>
+  </si>
+  <si>
+    <t>Ztrácíš balanc i důstojnost.</t>
+  </si>
+  <si>
+    <t>Miněš a skoro spadneš.</t>
+  </si>
+  <si>
+    <t>Na poslední chvíli to ustojíš.</t>
+  </si>
+  <si>
+    <t>Uhodíš vlastní zbroj.</t>
+  </si>
+  <si>
+    <t>Tvůj útok narazí do tebe.</t>
+  </si>
+  <si>
+    <t>Zazvoní to víc než by mělo.</t>
+  </si>
+  <si>
+    <t>Zbraň se zasekne.</t>
+  </si>
+  <si>
+    <t>Zbraň se chytí do něčeho.</t>
+  </si>
+  <si>
+    <t>Chvíli ji taháš ven.</t>
+  </si>
+  <si>
+    <t>Ztratíš grip.</t>
+  </si>
+  <si>
+    <t>Ruka ti sklouzne.</t>
+  </si>
+  <si>
+    <t>Útok nemá žádnou sílu.</t>
+  </si>
+  <si>
+    <t>Zavrávoráš.</t>
+  </si>
+  <si>
+    <t>Neudržíš rovnováhu.</t>
+  </si>
+  <si>
+    <t>Bojuješ spíš s gravitací.</t>
+  </si>
+  <si>
+    <t>Zamotá se ti ruka.</t>
+  </si>
+  <si>
+    <t>Pohyby jsou úplně mimo.</t>
+  </si>
+  <si>
+    <t>Vypadá to jako tanec.</t>
+  </si>
+  <si>
+    <t>Uděláš zbytečný kotoul.</t>
+  </si>
+  <si>
+    <t>Pokus o styl skončí trapně.</t>
+  </si>
+  <si>
+    <t>Prach se zvedne kolem tebe.</t>
+  </si>
+  <si>
+    <t>Miněš o metr.</t>
+  </si>
+  <si>
+    <t>Útok jde úplně vedle.</t>
+  </si>
+  <si>
+    <t>Soupeř ani nemusí uhnout.</t>
+  </si>
+  <si>
+    <t>Spustíš bojový monolog.</t>
+  </si>
+  <si>
+    <t>Mluvíš místo boje.</t>
+  </si>
+  <si>
+    <t>Soupeř čeká, až skončíš.</t>
+  </si>
+  <si>
+    <t>Uděláš teatrální pózu.</t>
+  </si>
+  <si>
+    <t>Zastavíš se uprostřed útoku.</t>
+  </si>
+  <si>
+    <t>Vypadáš epicky… ale neúčinně.</t>
+  </si>
+  <si>
+    <t>Zamíříš špatně.</t>
+  </si>
+  <si>
+    <t>Mineš cíl úplně.</t>
+  </si>
+  <si>
+    <t>Soupeř stojí vedle tebe.</t>
+  </si>
+  <si>
+    <t>Uhodíš do země.</t>
+  </si>
+  <si>
+    <t>Zbraň zarazíš do hlíny.</t>
+  </si>
+  <si>
+    <t>Musíš ji vytrhnout ven.</t>
+  </si>
+  <si>
+    <t>Ztratíš tempo.</t>
+  </si>
+  <si>
+    <t>Zastavíš se uprostřed pohybu.</t>
+  </si>
+  <si>
+    <t>Útok úplně vyšumí.</t>
+  </si>
+  <si>
+    <t>Zavřeš oči při útoku.</t>
+  </si>
+  <si>
+    <t>Nic netrefíš.</t>
+  </si>
+  <si>
+    <t>Poklekneš bez důvodu.</t>
+  </si>
+  <si>
+    <t>Vypadá to skoro jako prosba.</t>
+  </si>
+  <si>
+    <t>Otřeš se o nepřítele.</t>
+  </si>
+  <si>
+    <t>Kontakt je směšný.</t>
+  </si>
+  <si>
+    <t>Nikdo neutrpěl újmu.</t>
+  </si>
+  <si>
+    <t>Uděláš zbytečný výpad.</t>
+  </si>
+  <si>
+    <t>Vyletíš dopředu.</t>
+  </si>
+  <si>
+    <t>Úplně mineš cíl.</t>
+  </si>
+  <si>
+    <t>Zadrhneš se.</t>
+  </si>
+  <si>
+    <t>Pohyb se zasekne.</t>
+  </si>
+  <si>
+    <t>Vypadá to neobratně.</t>
+  </si>
+  <si>
+    <t>Zamáváš zbraní.</t>
+  </si>
+  <si>
+    <t>Útok nemá směr.</t>
+  </si>
+  <si>
+    <t>Spíš máváš než útočíš.</t>
+  </si>
+  <si>
+    <t>Nejsi si jistý směrem.</t>
+  </si>
+  <si>
+    <t>Útočíš jinam.</t>
+  </si>
+  <si>
+    <t>Uděláš otočku navíc.</t>
+  </si>
+  <si>
+    <t>Přehnaný pohyb.</t>
+  </si>
+  <si>
+    <t>Ztratíš cíl z očí.</t>
+  </si>
+  <si>
+    <t>Uděláš komický krok.</t>
+  </si>
+  <si>
+    <t>Pohyb vypadá divně.</t>
+  </si>
+  <si>
+    <t>Soupeř se pousměje.</t>
+  </si>
+  <si>
+    <t>Zadrhne se ti noha.</t>
+  </si>
+  <si>
+    <t>Švih není dokončen.</t>
+  </si>
+  <si>
+    <t>Zůstaneš stát.</t>
+  </si>
+  <si>
+    <t>Uděláš falešný útok.</t>
+  </si>
+  <si>
+    <t>Útok nemá sílu.</t>
+  </si>
+  <si>
+    <t>Nic se nestane.</t>
+  </si>
+  <si>
+    <t>Miněš úplně.</t>
+  </si>
+  <si>
+    <t>Útok jde vedle.</t>
+  </si>
+  <si>
+    <t>Soupeř si ani nevšimne.</t>
+  </si>
+  <si>
+    <t>Zadrhne se ti dech.</t>
+  </si>
+  <si>
+    <t>Na chvíli se zastavíš.</t>
+  </si>
+  <si>
+    <t>Útok nedokončíš.</t>
+  </si>
+  <si>
+    <t>Zakopneš o kámen.</t>
+  </si>
+  <si>
+    <t>Nevšimneš si překážky.</t>
+  </si>
+  <si>
+    <t>Skoro spadneš.</t>
+  </si>
+  <si>
+    <t>Zvedneš prach.</t>
+  </si>
+  <si>
+    <t>Útok víří vzduch.</t>
+  </si>
+  <si>
+    <t>Nezasáhne nic.</t>
+  </si>
+  <si>
+    <t>Ztratíš styl.</t>
+  </si>
+  <si>
+    <t>Pohyb je kostrbatý.</t>
+  </si>
+  <si>
+    <t>Uděláš krok zpět.</t>
+  </si>
+  <si>
+    <t>Místo útoku couvneš.</t>
+  </si>
+  <si>
+    <t>Ztratíš příležitost.</t>
+  </si>
+  <si>
+    <t>Miněš obloukem.</t>
+  </si>
+  <si>
+    <t>Široký švih mine cíl.</t>
+  </si>
+  <si>
+    <t>Zapomeneš dokončit útok.</t>
+  </si>
+  <si>
+    <t>Zastavíš se v půlce.</t>
+  </si>
+  <si>
+    <t>Uděláš příliš velký krok.</t>
+  </si>
+  <si>
+    <t>Přestřelíš vzdálenost.</t>
+  </si>
+  <si>
+    <t>Útok je mimo.</t>
+  </si>
+  <si>
+    <t>Ztratíš balanc.</t>
+  </si>
+  <si>
+    <t>Nakloníš se dopředu.</t>
+  </si>
+  <si>
+    <t>Sotva to ustojíš.</t>
+  </si>
+  <si>
+    <t>Uděláš komickou otočku.</t>
+  </si>
+  <si>
+    <t>Pohyb je přehnaný.</t>
+  </si>
+  <si>
+    <t>Uhodíš do vzduchu vedle hlavy.</t>
+  </si>
+  <si>
+    <t>Blízko, ale mimo.</t>
+  </si>
+  <si>
+    <t>Soupeř se ani nehne.</t>
+  </si>
+  <si>
+    <t>Zasekneš se v pohybu.</t>
+  </si>
+  <si>
+    <t>Nejdeš dál.</t>
+  </si>
+  <si>
+    <t>Útok končí naprázdno.</t>
+  </si>
+  <si>
+    <t>Nejde to plynule.</t>
+  </si>
+  <si>
+    <t>Útok selže.</t>
+  </si>
+  <si>
+    <t>Uděláš divný krok.</t>
+  </si>
+  <si>
+    <t>Útok nemá efekt.</t>
+  </si>
+  <si>
+    <t>Zamáváš kolem sebe.</t>
+  </si>
+  <si>
+    <t>Útok nemá cíl.</t>
+  </si>
+  <si>
+    <t>Vypadá to chaoticky.</t>
+  </si>
+  <si>
+    <t>Miněš o vlásek.</t>
+  </si>
+  <si>
+    <t>Bylo to těsné.</t>
+  </si>
+  <si>
+    <t>Ale nestačilo to.</t>
+  </si>
+  <si>
+    <t>Ztratíš timing.</t>
+  </si>
+  <si>
+    <t>Reakce je pozdě.</t>
+  </si>
+  <si>
+    <t>Útok nevyjde.</t>
+  </si>
+  <si>
+    <t>Šíp vystřelí úplně mimo.</t>
+  </si>
+  <si>
+    <t>Tvůj výstřel letí kdoví kam.</t>
+  </si>
+  <si>
+    <t>Možná jsi právě trefil strom někde daleko.</t>
+  </si>
+  <si>
+    <t>Tětiva ti uklouzne.</t>
+  </si>
+  <si>
+    <t>Výstřel je slabý a nepřesný.</t>
+  </si>
+  <si>
+    <t>Šíp sotva opustí luk.</t>
+  </si>
+  <si>
+    <t>Šíp spadne hned před tebe.</t>
+  </si>
+  <si>
+    <t>Napneš luk… a nic.</t>
+  </si>
+  <si>
+    <t>Šíp jen trapně spadne k nohám.</t>
+  </si>
+  <si>
+    <t>Míříš úplně špatně.</t>
+  </si>
+  <si>
+    <t>Zaměříš vedle cíle.</t>
+  </si>
+  <si>
+    <t>Výstřel mine o několik metrů.</t>
+  </si>
+  <si>
+    <t>Zakopneš při střelbě.</t>
+  </si>
+  <si>
+    <t>Výstřel jde úplně mimo.</t>
+  </si>
+  <si>
+    <t>Uděláš dramatický výstřel.</t>
+  </si>
+  <si>
+    <t>Póza je perfektní.</t>
+  </si>
+  <si>
+    <t>Zásah nulový.</t>
+  </si>
+  <si>
+    <t>Tětiva tě plácne do ruky.</t>
+  </si>
+  <si>
+    <t>Ucukneš bolestí.</t>
+  </si>
+  <si>
+    <t>Výstřel selže.</t>
+  </si>
+  <si>
+    <t>Šíp se otočí ve vzduchu.</t>
+  </si>
+  <si>
+    <t>Let je divný.</t>
+  </si>
+  <si>
+    <t>Trajektorie nedává smysl.</t>
+  </si>
+  <si>
+    <t>Zapomeneš pustit tětivu.</t>
+  </si>
+  <si>
+    <t>Držíš napnutý luk.</t>
+  </si>
+  <si>
+    <t>A nic se nestane.</t>
+  </si>
+  <si>
+    <t>Vystřelíš příliš brzy.</t>
+  </si>
+  <si>
+    <t>Nedokončíš zamíření.</t>
+  </si>
+  <si>
+    <t>Šíp mine.</t>
+  </si>
+  <si>
+    <t>Zamotá se ti prst.</t>
+  </si>
+  <si>
+    <t>Výstřel není čistý.</t>
+  </si>
+  <si>
+    <t>Šíp letí bokem.</t>
+  </si>
+  <si>
+    <t>Šíp narazí do překážky.</t>
+  </si>
+  <si>
+    <t>Cesta není čistá.</t>
+  </si>
+  <si>
+    <t>Střela se zastaví.</t>
+  </si>
+  <si>
+    <t>Míříš na špatný cíl.</t>
+  </si>
+  <si>
+    <t>Zaměříš úplně jinam.</t>
+  </si>
+  <si>
+    <t>Výstřel je zbytečný.</t>
+  </si>
+  <si>
+    <t>Upustíš šíp.</t>
+  </si>
+  <si>
+    <t>Vypadne ti z ruky.</t>
+  </si>
+  <si>
+    <t>Musíš ho zvednout.</t>
+  </si>
+  <si>
+    <t>Zamíříš na vlastní nohu.</t>
+  </si>
+  <si>
+    <t>Rychle přehodnotíš směr.</t>
+  </si>
+  <si>
+    <t>Výstřel radši ani neproběhne.</t>
+  </si>
+  <si>
+    <t>Šíp se odrazí.</t>
+  </si>
+  <si>
+    <t>Zvláštní úhel.</t>
+  </si>
+  <si>
+    <t>Vystřelíš moc vysoko.</t>
+  </si>
+  <si>
+    <t>Šíp mizí na obloze.</t>
+  </si>
+  <si>
+    <t>Trefíš možná ptáka.</t>
+  </si>
+  <si>
+    <t>Nakloníš se.</t>
+  </si>
+  <si>
+    <t>Výstřel mine.</t>
+  </si>
+  <si>
+    <t>Zavřeš oči.</t>
+  </si>
+  <si>
+    <t>Výstřel je naslepo.</t>
+  </si>
+  <si>
+    <t>Ale fakt naslepo.</t>
+  </si>
+  <si>
+    <t>Vystřelíš pozdě.</t>
+  </si>
+  <si>
+    <t>Cíl už není tam.</t>
+  </si>
+  <si>
+    <t>Šíp letí do prázdna.</t>
+  </si>
+  <si>
+    <t>Šíp ti sklouzne.</t>
+  </si>
+  <si>
+    <t>Není správně nasazen.</t>
+  </si>
+  <si>
+    <t>Tětiva vydá divný zvuk.</t>
+  </si>
+  <si>
+    <t>Zaskočí tě to.</t>
+  </si>
+  <si>
+    <t>Výstřel pokazíš.</t>
+  </si>
+  <si>
+    <t>Míříš moc dlouho.</t>
+  </si>
+  <si>
+    <t>Přemýšlíš až moc.</t>
+  </si>
+  <si>
+    <t>A mineš.</t>
+  </si>
+  <si>
+    <t>Zapomeneš na dech.</t>
+  </si>
+  <si>
+    <t>Rozhodí tě to.</t>
+  </si>
+  <si>
+    <t>Výstřel není přesný.</t>
+  </si>
+  <si>
+    <t>Vystřelíš slabě.</t>
+  </si>
+  <si>
+    <t>Šíp nemá sílu.</t>
+  </si>
+  <si>
+    <t>Nedolétne.</t>
+  </si>
+  <si>
+    <t>Zadrhne se ti ruka.</t>
+  </si>
+  <si>
+    <t>Luk ti klouže.</t>
+  </si>
+  <si>
+    <t>Vystřelíš do země.</t>
+  </si>
+  <si>
+    <t>Špatný úhel.</t>
+  </si>
+  <si>
+    <t>Šíp zapíchneš pod sebe.</t>
+  </si>
+  <si>
+    <t>Zamíříš vedle.</t>
+  </si>
+  <si>
+    <t>Není to ani blízko.</t>
+  </si>
+  <si>
+    <t>Cíl je v pohodě.</t>
+  </si>
+  <si>
+    <t>Šíp letí divně.</t>
+  </si>
+  <si>
+    <t>Trajektorie je křivá.</t>
+  </si>
+  <si>
+    <t>Zadrhneš pohyb.</t>
+  </si>
+  <si>
+    <t>Nedokončíš výstřel.</t>
+  </si>
+  <si>
+    <t>Vystřelíš jinam.</t>
+  </si>
+  <si>
+    <t>Špatný směr.</t>
+  </si>
+  <si>
+    <t>Úplně mimo.</t>
+  </si>
+  <si>
+    <t>Míříš na zem.</t>
+  </si>
+  <si>
+    <t>Nechceš, ale stane se.</t>
+  </si>
+  <si>
+    <t>Šíp skončí dole.</t>
+  </si>
+  <si>
+    <t>Myšlenky utečou.</t>
+  </si>
+  <si>
+    <t>A šíp taky.</t>
+  </si>
+  <si>
+    <t>Vystřelíš s otočkou.</t>
+  </si>
+  <si>
+    <t>Styl &gt; přesnost.</t>
+  </si>
+  <si>
+    <t>Zamíříš mimo cíl.</t>
+  </si>
+  <si>
+    <t>Pozdě si to uvědomíš.</t>
+  </si>
+  <si>
+    <t>Už je vystřeleno.</t>
+  </si>
+  <si>
+    <t>Šíp spadne.</t>
+  </si>
+  <si>
+    <t>Nemá energii.</t>
+  </si>
+  <si>
+    <t>Zapomeneš natáhnout luk.</t>
+  </si>
+  <si>
+    <t>Vystřelíš bez síly.</t>
+  </si>
+  <si>
+    <t>Zadrhne se tětiva.</t>
+  </si>
+  <si>
+    <t>Zamíříš za cíl.</t>
+  </si>
+  <si>
+    <t>Přestřelíš.</t>
+  </si>
+  <si>
+    <t>Netrefíš nic.</t>
+  </si>
+  <si>
+    <t>Ztratíš postoj.</t>
+  </si>
+  <si>
+    <t>Nejsi stabilní.</t>
+  </si>
+  <si>
+    <t>Vystřelíš příliš rychle.</t>
+  </si>
+  <si>
+    <t>Bez zaměření.</t>
+  </si>
+  <si>
+    <t>Mineš.</t>
+  </si>
+  <si>
+    <t>Šíp se kýve.</t>
+  </si>
+  <si>
+    <t>Let není stabilní.</t>
+  </si>
+  <si>
+    <t>Zapomeneš dýchat.</t>
+  </si>
+  <si>
+    <t>Ztuhneš.</t>
+  </si>
+  <si>
+    <t>Výstřel je špatný.</t>
+  </si>
+  <si>
+    <t>Míříš jinam.</t>
+  </si>
+  <si>
+    <t>Cíl je jinde.</t>
+  </si>
+  <si>
+    <t>Šíp taky.</t>
+  </si>
+  <si>
+    <t>Pozdě vystřelíš.</t>
+  </si>
+  <si>
+    <t>Zadrhneš loket.</t>
+  </si>
+  <si>
+    <t>Vystřelíš do prázdna.</t>
+  </si>
+  <si>
+    <t>Nikdo tam není.</t>
+  </si>
+  <si>
+    <t>Zbytečný šíp.</t>
+  </si>
+  <si>
+    <t>Nesoustředíš se.</t>
+  </si>
+  <si>
+    <t>Mineš dramaticky.</t>
+  </si>
+  <si>
+    <t>Vypadá to dobře.</t>
+  </si>
+  <si>
+    <t>Ale mineš.</t>
+  </si>
+  <si>
+    <t>Zakryješ si oči.</t>
+  </si>
+  <si>
+    <t>Nevidíš útok.</t>
+  </si>
+  <si>
+    <t>Blokuješ špatným směrem.</t>
+  </si>
+  <si>
+    <t>Bráníš se vedle.</t>
+  </si>
+  <si>
+    <t>Útok jde jinudy.</t>
+  </si>
+  <si>
+    <t>Uhneš… do útoku.</t>
+  </si>
+  <si>
+    <t>Trefíš se sám.</t>
+  </si>
+  <si>
+    <t>Zakopneš při obraně.</t>
+  </si>
+  <si>
+    <t>Obrana nefunguje.</t>
+  </si>
+  <si>
+    <t>Zvedneš ruce pozdě.</t>
+  </si>
+  <si>
+    <t>Útok projde.</t>
+  </si>
+  <si>
+    <t>Uhneš příliš brzy.</t>
+  </si>
+  <si>
+    <t>Útok tě dožene.</t>
+  </si>
+  <si>
+    <t>Nemůžeš bránit.</t>
+  </si>
+  <si>
+    <t>Zamrzneš.</t>
+  </si>
+  <si>
+    <t>Neuděláš nic.</t>
+  </si>
+  <si>
+    <t>Útok tě překvapí.</t>
+  </si>
+  <si>
+    <t>Zakryješ špatnou stranu.</t>
+  </si>
+  <si>
+    <t>Nechráníš správně.</t>
+  </si>
+  <si>
+    <t>Zbytečná obrana.</t>
+  </si>
+  <si>
+    <t>Uděláš otočku.</t>
+  </si>
+  <si>
+    <t>Ztratíš přehled.</t>
+  </si>
+  <si>
+    <t>Upadneš.</t>
+  </si>
+  <si>
+    <t>Obrana končí.</t>
+  </si>
+  <si>
+    <t>Jsi na zemi.</t>
+  </si>
+  <si>
+    <t>Zvedneš štít pozdě.</t>
+  </si>
+  <si>
+    <t>Nic neblokuješ.</t>
+  </si>
+  <si>
+    <t>Uhneš do strany… kde je útok.</t>
+  </si>
+  <si>
+    <t>Zásah jistý.</t>
+  </si>
+  <si>
+    <t>Zamotá se ti noha.</t>
+  </si>
+  <si>
+    <t>Útok tě zasáhne.</t>
+  </si>
+  <si>
+    <t>Nesleduješ útok.</t>
+  </si>
+  <si>
+    <t>Obrana selže.</t>
+  </si>
+  <si>
+    <t>Zvedneš zbraň špatně.</t>
+  </si>
+  <si>
+    <t>Nechrání tě.</t>
+  </si>
+  <si>
+    <t>Zásah přichází.</t>
+  </si>
+  <si>
+    <t>Uhneš pozdě.</t>
+  </si>
+  <si>
+    <t>Nestihneš to.</t>
+  </si>
+  <si>
+    <t>Zakryješ si obličej.</t>
+  </si>
+  <si>
+    <t>Zbytečně.</t>
+  </si>
+  <si>
+    <t>Zbytek těla odkrytý.</t>
+  </si>
+  <si>
+    <t>Pohyby nesedí.</t>
+  </si>
+  <si>
+    <t>Zapomeneš reagovat.</t>
+  </si>
+  <si>
+    <t>Uhneš moc.</t>
+  </si>
+  <si>
+    <t>Odkryješ se.</t>
+  </si>
+  <si>
+    <t>Zakopneš dozadu.</t>
+  </si>
+  <si>
+    <t>Pád.</t>
+  </si>
+  <si>
+    <t>Konec obrany.</t>
+  </si>
+  <si>
+    <t>Zvedneš ruce špatně.</t>
+  </si>
+  <si>
+    <t>Nechráníš nic.</t>
+  </si>
+  <si>
+    <t>Není stabilita.</t>
+  </si>
+  <si>
+    <t>Uhneš špatným směrem.</t>
+  </si>
+  <si>
+    <t>Přesně do rány.</t>
+  </si>
+  <si>
+    <t>Smůla.</t>
+  </si>
+  <si>
+    <t>Zasekneš se.</t>
+  </si>
+  <si>
+    <t>Pohyb nepokračuje.</t>
+  </si>
+  <si>
+    <t>Zvedneš štít moc vysoko.</t>
+  </si>
+  <si>
+    <t>Spodek odkrytý.</t>
+  </si>
+  <si>
+    <t>Zásah.</t>
+  </si>
+  <si>
+    <t>Zakryješ si ruce.</t>
+  </si>
+  <si>
+    <t>Tělo odkryté.</t>
+  </si>
+  <si>
+    <t>Nevíš odkud útok jde.</t>
+  </si>
+  <si>
+    <t>A neubráníš se.</t>
+  </si>
+  <si>
+    <t>Kolísáš.</t>
+  </si>
+  <si>
+    <t>Neubráníš se.</t>
+  </si>
+  <si>
+    <t>Uhneš dopředu.</t>
+  </si>
+  <si>
+    <t>Špatná volba.</t>
+  </si>
+  <si>
+    <t>Jdeš do útoku.</t>
+  </si>
+  <si>
+    <t>Zvedneš nohu.</t>
+  </si>
+  <si>
+    <t>Nevhodně.</t>
+  </si>
+  <si>
+    <t>Zamrzneš v panice.</t>
+  </si>
+  <si>
+    <t>Zakryješ špatnou část.</t>
+  </si>
+  <si>
+    <t>Odkrytý zbytek.</t>
+  </si>
+  <si>
+    <t>Neudržíš obranu.</t>
+  </si>
+  <si>
+    <t>Zakopneš o sebe.</t>
+  </si>
+  <si>
+    <t>Uhneš pomalu.</t>
+  </si>
+  <si>
+    <t>Nestihneš.</t>
+  </si>
+  <si>
+    <t>Příliš pozdě.</t>
+  </si>
+  <si>
+    <t>Nevíš kam jít.</t>
+  </si>
+  <si>
+    <t>Zakryješ jen část.</t>
+  </si>
+  <si>
+    <t>Zbytek odkrytý.</t>
+  </si>
+  <si>
+    <t>Ztratíš rytmus boje.</t>
+  </si>
+  <si>
+    <t>Obrana padá.</t>
+  </si>
+  <si>
+    <t>Zamotá se ti krok.</t>
+  </si>
+  <si>
+    <t>Neudržíš stabilitu.</t>
+  </si>
+  <si>
+    <t>Zvedneš štít vedle.</t>
+  </si>
+  <si>
+    <t>Mimo směr útoku.</t>
+  </si>
+  <si>
+    <t>Uhneš úplně mimo.</t>
+  </si>
+  <si>
+    <t>Nechráníš se.</t>
+  </si>
+  <si>
+    <t>Myšlenky jinde.</t>
+  </si>
+  <si>
+    <t>Zakryješ si hlavu.</t>
+  </si>
+  <si>
+    <t>Uhneš špatně.</t>
+  </si>
+  <si>
+    <t>Do rány.</t>
+  </si>
+  <si>
+    <t>Bolí to.</t>
   </si>
 </sst>
 </file>
@@ -8537,7 +9605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F282"/>
+  <dimension ref="A1:F382"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -14189,6 +15257,2006 @@
         <v>1</v>
       </c>
     </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>6</v>
+      </c>
+      <c r="B283" t="s">
+        <v>885</v>
+      </c>
+      <c r="C283" t="s">
+        <v>890</v>
+      </c>
+      <c r="D283" t="s">
+        <v>2731</v>
+      </c>
+      <c r="E283" t="s">
+        <v>2732</v>
+      </c>
+      <c r="F283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>6</v>
+      </c>
+      <c r="B284" t="s">
+        <v>885</v>
+      </c>
+      <c r="C284" t="s">
+        <v>2733</v>
+      </c>
+      <c r="D284" t="s">
+        <v>2734</v>
+      </c>
+      <c r="E284" t="s">
+        <v>2735</v>
+      </c>
+      <c r="F284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>6</v>
+      </c>
+      <c r="B285" t="s">
+        <v>885</v>
+      </c>
+      <c r="C285" t="s">
+        <v>2736</v>
+      </c>
+      <c r="D285" t="s">
+        <v>2737</v>
+      </c>
+      <c r="E285" t="s">
+        <v>2738</v>
+      </c>
+      <c r="F285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>6</v>
+      </c>
+      <c r="B286" t="s">
+        <v>885</v>
+      </c>
+      <c r="C286" t="s">
+        <v>2739</v>
+      </c>
+      <c r="D286" t="s">
+        <v>2740</v>
+      </c>
+      <c r="E286" t="s">
+        <v>2741</v>
+      </c>
+      <c r="F286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>6</v>
+      </c>
+      <c r="B287" t="s">
+        <v>885</v>
+      </c>
+      <c r="C287" t="s">
+        <v>2742</v>
+      </c>
+      <c r="D287" t="s">
+        <v>2743</v>
+      </c>
+      <c r="E287" t="s">
+        <v>2744</v>
+      </c>
+      <c r="F287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>6</v>
+      </c>
+      <c r="B288" t="s">
+        <v>885</v>
+      </c>
+      <c r="C288" t="s">
+        <v>2745</v>
+      </c>
+      <c r="D288" t="s">
+        <v>2746</v>
+      </c>
+      <c r="E288" t="s">
+        <v>2747</v>
+      </c>
+      <c r="F288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>6</v>
+      </c>
+      <c r="B289" t="s">
+        <v>885</v>
+      </c>
+      <c r="C289" t="s">
+        <v>2748</v>
+      </c>
+      <c r="D289" t="s">
+        <v>2749</v>
+      </c>
+      <c r="E289" t="s">
+        <v>2750</v>
+      </c>
+      <c r="F289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>6</v>
+      </c>
+      <c r="B290" t="s">
+        <v>885</v>
+      </c>
+      <c r="C290" t="s">
+        <v>2751</v>
+      </c>
+      <c r="D290" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E290" t="s">
+        <v>2752</v>
+      </c>
+      <c r="F290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>6</v>
+      </c>
+      <c r="B291" t="s">
+        <v>885</v>
+      </c>
+      <c r="C291" t="s">
+        <v>2753</v>
+      </c>
+      <c r="D291" t="s">
+        <v>2754</v>
+      </c>
+      <c r="E291" t="s">
+        <v>2755</v>
+      </c>
+      <c r="F291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>6</v>
+      </c>
+      <c r="B292" t="s">
+        <v>885</v>
+      </c>
+      <c r="C292" t="s">
+        <v>2756</v>
+      </c>
+      <c r="D292" t="s">
+        <v>2757</v>
+      </c>
+      <c r="E292" t="s">
+        <v>2758</v>
+      </c>
+      <c r="F292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>6</v>
+      </c>
+      <c r="B293" t="s">
+        <v>885</v>
+      </c>
+      <c r="C293" t="s">
+        <v>2759</v>
+      </c>
+      <c r="D293" t="s">
+        <v>2760</v>
+      </c>
+      <c r="E293" t="s">
+        <v>2761</v>
+      </c>
+      <c r="F293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>6</v>
+      </c>
+      <c r="B294" t="s">
+        <v>885</v>
+      </c>
+      <c r="C294" t="s">
+        <v>2762</v>
+      </c>
+      <c r="D294" t="s">
+        <v>2763</v>
+      </c>
+      <c r="E294" t="s">
+        <v>2764</v>
+      </c>
+      <c r="F294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>6</v>
+      </c>
+      <c r="B295" t="s">
+        <v>885</v>
+      </c>
+      <c r="C295" t="s">
+        <v>2765</v>
+      </c>
+      <c r="D295" t="s">
+        <v>2766</v>
+      </c>
+      <c r="E295" t="s">
+        <v>2767</v>
+      </c>
+      <c r="F295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>6</v>
+      </c>
+      <c r="B296" t="s">
+        <v>885</v>
+      </c>
+      <c r="C296" t="s">
+        <v>2768</v>
+      </c>
+      <c r="D296" t="s">
+        <v>2769</v>
+      </c>
+      <c r="E296" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>6</v>
+      </c>
+      <c r="B297" t="s">
+        <v>885</v>
+      </c>
+      <c r="C297" t="s">
+        <v>2771</v>
+      </c>
+      <c r="D297" t="s">
+        <v>2772</v>
+      </c>
+      <c r="E297" t="s">
+        <v>2773</v>
+      </c>
+      <c r="F297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>6</v>
+      </c>
+      <c r="B298" t="s">
+        <v>885</v>
+      </c>
+      <c r="C298" t="s">
+        <v>2774</v>
+      </c>
+      <c r="D298" t="s">
+        <v>2775</v>
+      </c>
+      <c r="E298" t="s">
+        <v>2776</v>
+      </c>
+      <c r="F298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>6</v>
+      </c>
+      <c r="B299" t="s">
+        <v>885</v>
+      </c>
+      <c r="C299" t="s">
+        <v>2777</v>
+      </c>
+      <c r="D299" t="s">
+        <v>2778</v>
+      </c>
+      <c r="E299" t="s">
+        <v>2779</v>
+      </c>
+      <c r="F299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>6</v>
+      </c>
+      <c r="B300" t="s">
+        <v>885</v>
+      </c>
+      <c r="C300" t="s">
+        <v>2780</v>
+      </c>
+      <c r="D300" t="s">
+        <v>2781</v>
+      </c>
+      <c r="E300" t="s">
+        <v>2782</v>
+      </c>
+      <c r="F300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>6</v>
+      </c>
+      <c r="B301" t="s">
+        <v>885</v>
+      </c>
+      <c r="C301" t="s">
+        <v>2783</v>
+      </c>
+      <c r="D301" t="s">
+        <v>2784</v>
+      </c>
+      <c r="E301" t="s">
+        <v>2785</v>
+      </c>
+      <c r="F301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>6</v>
+      </c>
+      <c r="B302" t="s">
+        <v>885</v>
+      </c>
+      <c r="C302" t="s">
+        <v>2786</v>
+      </c>
+      <c r="D302" t="s">
+        <v>2787</v>
+      </c>
+      <c r="E302" t="s">
+        <v>2788</v>
+      </c>
+      <c r="F302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>6</v>
+      </c>
+      <c r="B303" t="s">
+        <v>885</v>
+      </c>
+      <c r="C303" t="s">
+        <v>2789</v>
+      </c>
+      <c r="D303" t="s">
+        <v>2397</v>
+      </c>
+      <c r="E303" t="s">
+        <v>2790</v>
+      </c>
+      <c r="F303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>6</v>
+      </c>
+      <c r="B304" t="s">
+        <v>885</v>
+      </c>
+      <c r="C304" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D304" t="s">
+        <v>2791</v>
+      </c>
+      <c r="E304" t="s">
+        <v>2792</v>
+      </c>
+      <c r="F304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>6</v>
+      </c>
+      <c r="B305" t="s">
+        <v>885</v>
+      </c>
+      <c r="C305" t="s">
+        <v>2793</v>
+      </c>
+      <c r="D305" t="s">
+        <v>2794</v>
+      </c>
+      <c r="E305" t="s">
+        <v>2795</v>
+      </c>
+      <c r="F305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>6</v>
+      </c>
+      <c r="B306" t="s">
+        <v>885</v>
+      </c>
+      <c r="C306" t="s">
+        <v>2796</v>
+      </c>
+      <c r="D306" t="s">
+        <v>2797</v>
+      </c>
+      <c r="E306" t="s">
+        <v>2798</v>
+      </c>
+      <c r="F306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>6</v>
+      </c>
+      <c r="B307" t="s">
+        <v>885</v>
+      </c>
+      <c r="C307" t="s">
+        <v>2799</v>
+      </c>
+      <c r="D307" t="s">
+        <v>2800</v>
+      </c>
+      <c r="E307" t="s">
+        <v>2801</v>
+      </c>
+      <c r="F307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>6</v>
+      </c>
+      <c r="B308" t="s">
+        <v>885</v>
+      </c>
+      <c r="C308" t="s">
+        <v>2802</v>
+      </c>
+      <c r="D308" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E308" t="s">
+        <v>2804</v>
+      </c>
+      <c r="F308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>6</v>
+      </c>
+      <c r="B309" t="s">
+        <v>885</v>
+      </c>
+      <c r="C309" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D309" t="s">
+        <v>2805</v>
+      </c>
+      <c r="E309" t="s">
+        <v>2806</v>
+      </c>
+      <c r="F309">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>6</v>
+      </c>
+      <c r="B310" t="s">
+        <v>885</v>
+      </c>
+      <c r="C310" t="s">
+        <v>2807</v>
+      </c>
+      <c r="D310" t="s">
+        <v>2808</v>
+      </c>
+      <c r="E310" t="s">
+        <v>2809</v>
+      </c>
+      <c r="F310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>6</v>
+      </c>
+      <c r="B311" t="s">
+        <v>885</v>
+      </c>
+      <c r="C311" t="s">
+        <v>2810</v>
+      </c>
+      <c r="D311" t="s">
+        <v>2811</v>
+      </c>
+      <c r="E311" t="s">
+        <v>2812</v>
+      </c>
+      <c r="F311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>6</v>
+      </c>
+      <c r="B312" t="s">
+        <v>885</v>
+      </c>
+      <c r="C312" t="s">
+        <v>2813</v>
+      </c>
+      <c r="D312" t="s">
+        <v>2814</v>
+      </c>
+      <c r="E312" t="s">
+        <v>2815</v>
+      </c>
+      <c r="F312">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>6</v>
+      </c>
+      <c r="B313" t="s">
+        <v>885</v>
+      </c>
+      <c r="C313" t="s">
+        <v>2816</v>
+      </c>
+      <c r="D313" t="s">
+        <v>2817</v>
+      </c>
+      <c r="E313" t="s">
+        <v>2818</v>
+      </c>
+      <c r="F313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>6</v>
+      </c>
+      <c r="B314" t="s">
+        <v>885</v>
+      </c>
+      <c r="C314" t="s">
+        <v>2819</v>
+      </c>
+      <c r="D314" t="s">
+        <v>2820</v>
+      </c>
+      <c r="E314" t="s">
+        <v>2821</v>
+      </c>
+      <c r="F314">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>6</v>
+      </c>
+      <c r="B315" t="s">
+        <v>885</v>
+      </c>
+      <c r="C315" t="s">
+        <v>2822</v>
+      </c>
+      <c r="D315" t="s">
+        <v>2823</v>
+      </c>
+      <c r="E315" t="s">
+        <v>2824</v>
+      </c>
+      <c r="F315">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>6</v>
+      </c>
+      <c r="B316" t="s">
+        <v>885</v>
+      </c>
+      <c r="C316" t="s">
+        <v>2825</v>
+      </c>
+      <c r="D316" t="s">
+        <v>2826</v>
+      </c>
+      <c r="E316" t="s">
+        <v>2827</v>
+      </c>
+      <c r="F316">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>6</v>
+      </c>
+      <c r="B317" t="s">
+        <v>885</v>
+      </c>
+      <c r="C317" t="s">
+        <v>2828</v>
+      </c>
+      <c r="D317" t="s">
+        <v>2829</v>
+      </c>
+      <c r="E317" t="s">
+        <v>2830</v>
+      </c>
+      <c r="F317">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>6</v>
+      </c>
+      <c r="B318" t="s">
+        <v>885</v>
+      </c>
+      <c r="C318" t="s">
+        <v>2684</v>
+      </c>
+      <c r="D318" t="s">
+        <v>2808</v>
+      </c>
+      <c r="E318" t="s">
+        <v>2055</v>
+      </c>
+      <c r="F318">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>6</v>
+      </c>
+      <c r="B319" t="s">
+        <v>885</v>
+      </c>
+      <c r="C319" t="s">
+        <v>2831</v>
+      </c>
+      <c r="D319" t="s">
+        <v>2832</v>
+      </c>
+      <c r="E319" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F319">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>6</v>
+      </c>
+      <c r="B320" t="s">
+        <v>885</v>
+      </c>
+      <c r="C320" t="s">
+        <v>2833</v>
+      </c>
+      <c r="D320" t="s">
+        <v>2834</v>
+      </c>
+      <c r="E320" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F320">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>6</v>
+      </c>
+      <c r="B321" t="s">
+        <v>885</v>
+      </c>
+      <c r="C321" t="s">
+        <v>2836</v>
+      </c>
+      <c r="D321" t="s">
+        <v>2837</v>
+      </c>
+      <c r="E321" t="s">
+        <v>2790</v>
+      </c>
+      <c r="F321">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>6</v>
+      </c>
+      <c r="B322" t="s">
+        <v>885</v>
+      </c>
+      <c r="C322" t="s">
+        <v>2838</v>
+      </c>
+      <c r="D322" t="s">
+        <v>2839</v>
+      </c>
+      <c r="E322" t="s">
+        <v>2501</v>
+      </c>
+      <c r="F322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>6</v>
+      </c>
+      <c r="B323" t="s">
+        <v>885</v>
+      </c>
+      <c r="C323" t="s">
+        <v>2840</v>
+      </c>
+      <c r="D323" t="s">
+        <v>2841</v>
+      </c>
+      <c r="E323" t="s">
+        <v>2842</v>
+      </c>
+      <c r="F323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>6</v>
+      </c>
+      <c r="B324" t="s">
+        <v>885</v>
+      </c>
+      <c r="C324" t="s">
+        <v>2843</v>
+      </c>
+      <c r="D324" t="s">
+        <v>2844</v>
+      </c>
+      <c r="E324" t="s">
+        <v>2845</v>
+      </c>
+      <c r="F324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>6</v>
+      </c>
+      <c r="B325" t="s">
+        <v>885</v>
+      </c>
+      <c r="C325" t="s">
+        <v>2846</v>
+      </c>
+      <c r="D325" t="s">
+        <v>2847</v>
+      </c>
+      <c r="E325" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>6</v>
+      </c>
+      <c r="B326" t="s">
+        <v>885</v>
+      </c>
+      <c r="C326" t="s">
+        <v>2848</v>
+      </c>
+      <c r="D326" t="s">
+        <v>2849</v>
+      </c>
+      <c r="E326" t="s">
+        <v>2850</v>
+      </c>
+      <c r="F326">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>6</v>
+      </c>
+      <c r="B327" t="s">
+        <v>885</v>
+      </c>
+      <c r="C327" t="s">
+        <v>2851</v>
+      </c>
+      <c r="D327" t="s">
+        <v>2852</v>
+      </c>
+      <c r="E327" t="s">
+        <v>2853</v>
+      </c>
+      <c r="F327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>6</v>
+      </c>
+      <c r="B328" t="s">
+        <v>885</v>
+      </c>
+      <c r="C328" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D328" t="s">
+        <v>2854</v>
+      </c>
+      <c r="E328" t="s">
+        <v>2855</v>
+      </c>
+      <c r="F328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>6</v>
+      </c>
+      <c r="B329" t="s">
+        <v>885</v>
+      </c>
+      <c r="C329" t="s">
+        <v>2856</v>
+      </c>
+      <c r="D329" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E329" t="s">
+        <v>2857</v>
+      </c>
+      <c r="F329">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>6</v>
+      </c>
+      <c r="B330" t="s">
+        <v>885</v>
+      </c>
+      <c r="C330" t="s">
+        <v>2858</v>
+      </c>
+      <c r="D330" t="s">
+        <v>2859</v>
+      </c>
+      <c r="E330" t="s">
+        <v>2860</v>
+      </c>
+      <c r="F330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>6</v>
+      </c>
+      <c r="B331" t="s">
+        <v>885</v>
+      </c>
+      <c r="C331" t="s">
+        <v>2861</v>
+      </c>
+      <c r="D331" t="s">
+        <v>2862</v>
+      </c>
+      <c r="E331" t="s">
+        <v>2863</v>
+      </c>
+      <c r="F331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>6</v>
+      </c>
+      <c r="B332" t="s">
+        <v>885</v>
+      </c>
+      <c r="C332" t="s">
+        <v>2864</v>
+      </c>
+      <c r="D332" t="s">
+        <v>2865</v>
+      </c>
+      <c r="E332" t="s">
+        <v>2866</v>
+      </c>
+      <c r="F332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>28</v>
+      </c>
+      <c r="B333" t="s">
+        <v>885</v>
+      </c>
+      <c r="C333" t="s">
+        <v>2867</v>
+      </c>
+      <c r="D333" t="s">
+        <v>2868</v>
+      </c>
+      <c r="E333" t="s">
+        <v>2869</v>
+      </c>
+      <c r="F333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>28</v>
+      </c>
+      <c r="B334" t="s">
+        <v>885</v>
+      </c>
+      <c r="C334" t="s">
+        <v>2870</v>
+      </c>
+      <c r="D334" t="s">
+        <v>2871</v>
+      </c>
+      <c r="E334" t="s">
+        <v>2872</v>
+      </c>
+      <c r="F334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>28</v>
+      </c>
+      <c r="B335" t="s">
+        <v>885</v>
+      </c>
+      <c r="C335" t="s">
+        <v>2873</v>
+      </c>
+      <c r="D335" t="s">
+        <v>2874</v>
+      </c>
+      <c r="E335" t="s">
+        <v>2875</v>
+      </c>
+      <c r="F335">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>28</v>
+      </c>
+      <c r="B336" t="s">
+        <v>885</v>
+      </c>
+      <c r="C336" t="s">
+        <v>2876</v>
+      </c>
+      <c r="D336" t="s">
+        <v>2877</v>
+      </c>
+      <c r="E336" t="s">
+        <v>2878</v>
+      </c>
+      <c r="F336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>28</v>
+      </c>
+      <c r="B337" t="s">
+        <v>885</v>
+      </c>
+      <c r="C337" t="s">
+        <v>2879</v>
+      </c>
+      <c r="D337" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E337" t="s">
+        <v>2880</v>
+      </c>
+      <c r="F337">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>28</v>
+      </c>
+      <c r="B338" t="s">
+        <v>885</v>
+      </c>
+      <c r="C338" t="s">
+        <v>2881</v>
+      </c>
+      <c r="D338" t="s">
+        <v>2882</v>
+      </c>
+      <c r="E338" t="s">
+        <v>2883</v>
+      </c>
+      <c r="F338">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>28</v>
+      </c>
+      <c r="B339" t="s">
+        <v>885</v>
+      </c>
+      <c r="C339" t="s">
+        <v>2884</v>
+      </c>
+      <c r="D339" t="s">
+        <v>2885</v>
+      </c>
+      <c r="E339" t="s">
+        <v>2886</v>
+      </c>
+      <c r="F339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>28</v>
+      </c>
+      <c r="B340" t="s">
+        <v>885</v>
+      </c>
+      <c r="C340" t="s">
+        <v>2887</v>
+      </c>
+      <c r="D340" t="s">
+        <v>2888</v>
+      </c>
+      <c r="E340" t="s">
+        <v>2889</v>
+      </c>
+      <c r="F340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>28</v>
+      </c>
+      <c r="B341" t="s">
+        <v>885</v>
+      </c>
+      <c r="C341" t="s">
+        <v>2890</v>
+      </c>
+      <c r="D341" t="s">
+        <v>2891</v>
+      </c>
+      <c r="E341" t="s">
+        <v>2892</v>
+      </c>
+      <c r="F341">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>28</v>
+      </c>
+      <c r="B342" t="s">
+        <v>885</v>
+      </c>
+      <c r="C342" t="s">
+        <v>2893</v>
+      </c>
+      <c r="D342" t="s">
+        <v>2894</v>
+      </c>
+      <c r="E342" t="s">
+        <v>2895</v>
+      </c>
+      <c r="F342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>28</v>
+      </c>
+      <c r="B343" t="s">
+        <v>885</v>
+      </c>
+      <c r="C343" t="s">
+        <v>2896</v>
+      </c>
+      <c r="D343" t="s">
+        <v>2897</v>
+      </c>
+      <c r="E343" t="s">
+        <v>2898</v>
+      </c>
+      <c r="F343">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>28</v>
+      </c>
+      <c r="B344" t="s">
+        <v>885</v>
+      </c>
+      <c r="C344" t="s">
+        <v>2899</v>
+      </c>
+      <c r="D344" t="s">
+        <v>2900</v>
+      </c>
+      <c r="E344" t="s">
+        <v>2901</v>
+      </c>
+      <c r="F344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>28</v>
+      </c>
+      <c r="B345" t="s">
+        <v>885</v>
+      </c>
+      <c r="C345" t="s">
+        <v>2902</v>
+      </c>
+      <c r="D345" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E345" t="s">
+        <v>2904</v>
+      </c>
+      <c r="F345">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>28</v>
+      </c>
+      <c r="B346" t="s">
+        <v>885</v>
+      </c>
+      <c r="C346" t="s">
+        <v>2905</v>
+      </c>
+      <c r="D346" t="s">
+        <v>2906</v>
+      </c>
+      <c r="E346" t="s">
+        <v>2907</v>
+      </c>
+      <c r="F346">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>28</v>
+      </c>
+      <c r="B347" t="s">
+        <v>885</v>
+      </c>
+      <c r="C347" t="s">
+        <v>2908</v>
+      </c>
+      <c r="D347" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E347" t="s">
+        <v>2910</v>
+      </c>
+      <c r="F347">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>28</v>
+      </c>
+      <c r="B348" t="s">
+        <v>885</v>
+      </c>
+      <c r="C348" t="s">
+        <v>2911</v>
+      </c>
+      <c r="D348" t="s">
+        <v>2912</v>
+      </c>
+      <c r="E348" t="s">
+        <v>2790</v>
+      </c>
+      <c r="F348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>28</v>
+      </c>
+      <c r="B349" t="s">
+        <v>885</v>
+      </c>
+      <c r="C349" t="s">
+        <v>2913</v>
+      </c>
+      <c r="D349" t="s">
+        <v>2914</v>
+      </c>
+      <c r="E349" t="s">
+        <v>2915</v>
+      </c>
+      <c r="F349">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>28</v>
+      </c>
+      <c r="B350" t="s">
+        <v>885</v>
+      </c>
+      <c r="C350" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D350" t="s">
+        <v>2916</v>
+      </c>
+      <c r="E350" t="s">
+        <v>2917</v>
+      </c>
+      <c r="F350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>28</v>
+      </c>
+      <c r="B351" t="s">
+        <v>885</v>
+      </c>
+      <c r="C351" t="s">
+        <v>2918</v>
+      </c>
+      <c r="D351" t="s">
+        <v>2919</v>
+      </c>
+      <c r="E351" t="s">
+        <v>2920</v>
+      </c>
+      <c r="F351">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>28</v>
+      </c>
+      <c r="B352" t="s">
+        <v>885</v>
+      </c>
+      <c r="C352" t="s">
+        <v>2921</v>
+      </c>
+      <c r="D352" t="s">
+        <v>2922</v>
+      </c>
+      <c r="E352" t="s">
+        <v>2923</v>
+      </c>
+      <c r="F352">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>28</v>
+      </c>
+      <c r="B353" t="s">
+        <v>885</v>
+      </c>
+      <c r="C353" t="s">
+        <v>2924</v>
+      </c>
+      <c r="D353" t="s">
+        <v>2925</v>
+      </c>
+      <c r="E353" t="s">
+        <v>2886</v>
+      </c>
+      <c r="F353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>28</v>
+      </c>
+      <c r="B354" t="s">
+        <v>885</v>
+      </c>
+      <c r="C354" t="s">
+        <v>2926</v>
+      </c>
+      <c r="D354" t="s">
+        <v>2927</v>
+      </c>
+      <c r="E354" t="s">
+        <v>2928</v>
+      </c>
+      <c r="F354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>28</v>
+      </c>
+      <c r="B355" t="s">
+        <v>885</v>
+      </c>
+      <c r="C355" t="s">
+        <v>2929</v>
+      </c>
+      <c r="D355" t="s">
+        <v>2930</v>
+      </c>
+      <c r="E355" t="s">
+        <v>2931</v>
+      </c>
+      <c r="F355">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>28</v>
+      </c>
+      <c r="B356" t="s">
+        <v>885</v>
+      </c>
+      <c r="C356" t="s">
+        <v>2932</v>
+      </c>
+      <c r="D356" t="s">
+        <v>2933</v>
+      </c>
+      <c r="E356" t="s">
+        <v>2934</v>
+      </c>
+      <c r="F356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>28</v>
+      </c>
+      <c r="B357" t="s">
+        <v>885</v>
+      </c>
+      <c r="C357" t="s">
+        <v>2935</v>
+      </c>
+      <c r="D357" t="s">
+        <v>2936</v>
+      </c>
+      <c r="E357" t="s">
+        <v>2937</v>
+      </c>
+      <c r="F357">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>28</v>
+      </c>
+      <c r="B358" t="s">
+        <v>885</v>
+      </c>
+      <c r="C358" t="s">
+        <v>2938</v>
+      </c>
+      <c r="D358" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E358" t="s">
+        <v>2886</v>
+      </c>
+      <c r="F358">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>28</v>
+      </c>
+      <c r="B359" t="s">
+        <v>885</v>
+      </c>
+      <c r="C359" t="s">
+        <v>2759</v>
+      </c>
+      <c r="D359" t="s">
+        <v>2939</v>
+      </c>
+      <c r="E359" t="s">
+        <v>2790</v>
+      </c>
+      <c r="F359">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>28</v>
+      </c>
+      <c r="B360" t="s">
+        <v>885</v>
+      </c>
+      <c r="C360" t="s">
+        <v>2940</v>
+      </c>
+      <c r="D360" t="s">
+        <v>2941</v>
+      </c>
+      <c r="E360" t="s">
+        <v>2942</v>
+      </c>
+      <c r="F360">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>28</v>
+      </c>
+      <c r="B361" t="s">
+        <v>885</v>
+      </c>
+      <c r="C361" t="s">
+        <v>2943</v>
+      </c>
+      <c r="D361" t="s">
+        <v>2944</v>
+      </c>
+      <c r="E361" t="s">
+        <v>2945</v>
+      </c>
+      <c r="F361">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>28</v>
+      </c>
+      <c r="B362" t="s">
+        <v>885</v>
+      </c>
+      <c r="C362" t="s">
+        <v>2946</v>
+      </c>
+      <c r="D362" t="s">
+        <v>2947</v>
+      </c>
+      <c r="E362" t="s">
+        <v>2790</v>
+      </c>
+      <c r="F362">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>28</v>
+      </c>
+      <c r="B363" t="s">
+        <v>885</v>
+      </c>
+      <c r="C363" t="s">
+        <v>2948</v>
+      </c>
+      <c r="D363" t="s">
+        <v>2949</v>
+      </c>
+      <c r="E363" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F363">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>28</v>
+      </c>
+      <c r="B364" t="s">
+        <v>885</v>
+      </c>
+      <c r="C364" t="s">
+        <v>2950</v>
+      </c>
+      <c r="D364" t="s">
+        <v>2951</v>
+      </c>
+      <c r="E364" t="s">
+        <v>2952</v>
+      </c>
+      <c r="F364">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>28</v>
+      </c>
+      <c r="B365" t="s">
+        <v>885</v>
+      </c>
+      <c r="C365" t="s">
+        <v>2953</v>
+      </c>
+      <c r="D365" t="s">
+        <v>2954</v>
+      </c>
+      <c r="E365" t="s">
+        <v>2955</v>
+      </c>
+      <c r="F365">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>28</v>
+      </c>
+      <c r="B366" t="s">
+        <v>885</v>
+      </c>
+      <c r="C366" t="s">
+        <v>1598</v>
+      </c>
+      <c r="D366" t="s">
+        <v>2956</v>
+      </c>
+      <c r="E366" t="s">
+        <v>2957</v>
+      </c>
+      <c r="F366">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>28</v>
+      </c>
+      <c r="B367" t="s">
+        <v>885</v>
+      </c>
+      <c r="C367" t="s">
+        <v>2958</v>
+      </c>
+      <c r="D367" t="s">
+        <v>2959</v>
+      </c>
+      <c r="E367" t="s">
+        <v>2931</v>
+      </c>
+      <c r="F367">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>28</v>
+      </c>
+      <c r="B368" t="s">
+        <v>885</v>
+      </c>
+      <c r="C368" t="s">
+        <v>2960</v>
+      </c>
+      <c r="D368" t="s">
+        <v>2961</v>
+      </c>
+      <c r="E368" t="s">
+        <v>2962</v>
+      </c>
+      <c r="F368">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>28</v>
+      </c>
+      <c r="B369" t="s">
+        <v>885</v>
+      </c>
+      <c r="C369" t="s">
+        <v>2963</v>
+      </c>
+      <c r="D369" t="s">
+        <v>2964</v>
+      </c>
+      <c r="E369" t="s">
+        <v>1779</v>
+      </c>
+      <c r="F369">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>28</v>
+      </c>
+      <c r="B370" t="s">
+        <v>885</v>
+      </c>
+      <c r="C370" t="s">
+        <v>2965</v>
+      </c>
+      <c r="D370" t="s">
+        <v>2966</v>
+      </c>
+      <c r="E370" t="s">
+        <v>2818</v>
+      </c>
+      <c r="F370">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>28</v>
+      </c>
+      <c r="B371" t="s">
+        <v>885</v>
+      </c>
+      <c r="C371" t="s">
+        <v>2967</v>
+      </c>
+      <c r="D371" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E371" t="s">
+        <v>2886</v>
+      </c>
+      <c r="F371">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>28</v>
+      </c>
+      <c r="B372" t="s">
+        <v>885</v>
+      </c>
+      <c r="C372" t="s">
+        <v>2968</v>
+      </c>
+      <c r="D372" t="s">
+        <v>2969</v>
+      </c>
+      <c r="E372" t="s">
+        <v>2970</v>
+      </c>
+      <c r="F372">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>28</v>
+      </c>
+      <c r="B373" t="s">
+        <v>885</v>
+      </c>
+      <c r="C373" t="s">
+        <v>2971</v>
+      </c>
+      <c r="D373" t="s">
+        <v>2972</v>
+      </c>
+      <c r="E373" t="s">
+        <v>2895</v>
+      </c>
+      <c r="F373">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>28</v>
+      </c>
+      <c r="B374" t="s">
+        <v>885</v>
+      </c>
+      <c r="C374" t="s">
+        <v>2973</v>
+      </c>
+      <c r="D374" t="s">
+        <v>2974</v>
+      </c>
+      <c r="E374" t="s">
+        <v>2975</v>
+      </c>
+      <c r="F374">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>28</v>
+      </c>
+      <c r="B375" t="s">
+        <v>885</v>
+      </c>
+      <c r="C375" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D375" t="s">
+        <v>2977</v>
+      </c>
+      <c r="E375" t="s">
+        <v>2883</v>
+      </c>
+      <c r="F375">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>28</v>
+      </c>
+      <c r="B376" t="s">
+        <v>885</v>
+      </c>
+      <c r="C376" t="s">
+        <v>2978</v>
+      </c>
+      <c r="D376" t="s">
+        <v>2979</v>
+      </c>
+      <c r="E376" t="s">
+        <v>2980</v>
+      </c>
+      <c r="F376">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>28</v>
+      </c>
+      <c r="B377" t="s">
+        <v>885</v>
+      </c>
+      <c r="C377" t="s">
+        <v>2981</v>
+      </c>
+      <c r="D377" t="s">
+        <v>2982</v>
+      </c>
+      <c r="E377" t="s">
+        <v>2983</v>
+      </c>
+      <c r="F377">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>28</v>
+      </c>
+      <c r="B378" t="s">
+        <v>885</v>
+      </c>
+      <c r="C378" t="s">
+        <v>2864</v>
+      </c>
+      <c r="D378" t="s">
+        <v>2984</v>
+      </c>
+      <c r="E378" t="s">
+        <v>2975</v>
+      </c>
+      <c r="F378">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>28</v>
+      </c>
+      <c r="B379" t="s">
+        <v>885</v>
+      </c>
+      <c r="C379" t="s">
+        <v>2985</v>
+      </c>
+      <c r="D379" t="s">
+        <v>654</v>
+      </c>
+      <c r="E379" t="s">
+        <v>2886</v>
+      </c>
+      <c r="F379">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>28</v>
+      </c>
+      <c r="B380" t="s">
+        <v>885</v>
+      </c>
+      <c r="C380" t="s">
+        <v>2986</v>
+      </c>
+      <c r="D380" t="s">
+        <v>2987</v>
+      </c>
+      <c r="E380" t="s">
+        <v>2988</v>
+      </c>
+      <c r="F380">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>28</v>
+      </c>
+      <c r="B381" t="s">
+        <v>885</v>
+      </c>
+      <c r="C381" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D381" t="s">
+        <v>2989</v>
+      </c>
+      <c r="E381" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F381">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>28</v>
+      </c>
+      <c r="B382" t="s">
+        <v>885</v>
+      </c>
+      <c r="C382" t="s">
+        <v>2990</v>
+      </c>
+      <c r="D382" t="s">
+        <v>2991</v>
+      </c>
+      <c r="E382" t="s">
+        <v>2992</v>
+      </c>
+      <c r="F382">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -14197,7 +17265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80CAE411-9ABA-4D2F-A12C-49D9B350EB7D}">
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E187"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
@@ -14206,7 +17274,7 @@
     <col min="4" max="4" width="36.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" customWidth="1"/>
+    <col min="13" max="13" width="6.5703125" customWidth="1"/>
     <col min="14" max="14" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -16536,6 +19604,856 @@
         <v>817</v>
       </c>
       <c r="E137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>885</v>
+      </c>
+      <c r="B138" t="s">
+        <v>2993</v>
+      </c>
+      <c r="C138" t="s">
+        <v>2048</v>
+      </c>
+      <c r="D138" t="s">
+        <v>2994</v>
+      </c>
+      <c r="E138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>885</v>
+      </c>
+      <c r="B139" t="s">
+        <v>2995</v>
+      </c>
+      <c r="C139" t="s">
+        <v>2996</v>
+      </c>
+      <c r="D139" t="s">
+        <v>2997</v>
+      </c>
+      <c r="E139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>885</v>
+      </c>
+      <c r="B140" t="s">
+        <v>2998</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D140" t="s">
+        <v>2999</v>
+      </c>
+      <c r="E140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>885</v>
+      </c>
+      <c r="B141" t="s">
+        <v>3000</v>
+      </c>
+      <c r="C141" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D141" t="s">
+        <v>3001</v>
+      </c>
+      <c r="E141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>885</v>
+      </c>
+      <c r="B142" t="s">
+        <v>3002</v>
+      </c>
+      <c r="C142" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D142" t="s">
+        <v>3003</v>
+      </c>
+      <c r="E142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>885</v>
+      </c>
+      <c r="B143" t="s">
+        <v>3004</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D143" t="s">
+        <v>3005</v>
+      </c>
+      <c r="E143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>885</v>
+      </c>
+      <c r="B144" t="s">
+        <v>2843</v>
+      </c>
+      <c r="C144" t="s">
+        <v>2916</v>
+      </c>
+      <c r="D144" t="s">
+        <v>3006</v>
+      </c>
+      <c r="E144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>885</v>
+      </c>
+      <c r="B145" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C145" t="s">
+        <v>3008</v>
+      </c>
+      <c r="D145" t="s">
+        <v>3009</v>
+      </c>
+      <c r="E145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>885</v>
+      </c>
+      <c r="B146" t="s">
+        <v>3010</v>
+      </c>
+      <c r="C146" t="s">
+        <v>3011</v>
+      </c>
+      <c r="D146" t="s">
+        <v>3012</v>
+      </c>
+      <c r="E146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>885</v>
+      </c>
+      <c r="B147" t="s">
+        <v>3013</v>
+      </c>
+      <c r="C147" t="s">
+        <v>3014</v>
+      </c>
+      <c r="D147" t="s">
+        <v>3003</v>
+      </c>
+      <c r="E147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>885</v>
+      </c>
+      <c r="B148" t="s">
+        <v>3015</v>
+      </c>
+      <c r="C148" t="s">
+        <v>3016</v>
+      </c>
+      <c r="D148" t="s">
+        <v>3017</v>
+      </c>
+      <c r="E148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>885</v>
+      </c>
+      <c r="B149" t="s">
+        <v>3018</v>
+      </c>
+      <c r="C149" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D149" t="s">
+        <v>3019</v>
+      </c>
+      <c r="E149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>885</v>
+      </c>
+      <c r="B150" t="s">
+        <v>3020</v>
+      </c>
+      <c r="C150" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D150" t="s">
+        <v>3021</v>
+      </c>
+      <c r="E150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>885</v>
+      </c>
+      <c r="B151" t="s">
+        <v>3022</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D151" t="s">
+        <v>3023</v>
+      </c>
+      <c r="E151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>885</v>
+      </c>
+      <c r="B152" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C152" t="s">
+        <v>3024</v>
+      </c>
+      <c r="D152" t="s">
+        <v>3025</v>
+      </c>
+      <c r="E152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>885</v>
+      </c>
+      <c r="B153" t="s">
+        <v>3026</v>
+      </c>
+      <c r="C153" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D153" t="s">
+        <v>3028</v>
+      </c>
+      <c r="E153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>885</v>
+      </c>
+      <c r="B154" t="s">
+        <v>3029</v>
+      </c>
+      <c r="C154" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D154" t="s">
+        <v>3030</v>
+      </c>
+      <c r="E154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>885</v>
+      </c>
+      <c r="B155" t="s">
+        <v>3031</v>
+      </c>
+      <c r="C155" t="s">
+        <v>3032</v>
+      </c>
+      <c r="D155" t="s">
+        <v>3033</v>
+      </c>
+      <c r="E155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>885</v>
+      </c>
+      <c r="B156" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C156" t="s">
+        <v>3034</v>
+      </c>
+      <c r="D156" t="s">
+        <v>3001</v>
+      </c>
+      <c r="E156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>885</v>
+      </c>
+      <c r="B157" t="s">
+        <v>3035</v>
+      </c>
+      <c r="C157" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D157" t="s">
+        <v>1684</v>
+      </c>
+      <c r="E157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>885</v>
+      </c>
+      <c r="B158" t="s">
+        <v>3036</v>
+      </c>
+      <c r="C158" t="s">
+        <v>3037</v>
+      </c>
+      <c r="D158" t="s">
+        <v>3003</v>
+      </c>
+      <c r="E158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>885</v>
+      </c>
+      <c r="B159" t="s">
+        <v>3038</v>
+      </c>
+      <c r="C159" t="s">
+        <v>3039</v>
+      </c>
+      <c r="D159" t="s">
+        <v>3040</v>
+      </c>
+      <c r="E159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>885</v>
+      </c>
+      <c r="B160" t="s">
+        <v>3041</v>
+      </c>
+      <c r="C160" t="s">
+        <v>3042</v>
+      </c>
+      <c r="D160" t="s">
+        <v>3003</v>
+      </c>
+      <c r="E160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>885</v>
+      </c>
+      <c r="B161" t="s">
+        <v>2971</v>
+      </c>
+      <c r="C161" t="s">
+        <v>3043</v>
+      </c>
+      <c r="D161" t="s">
+        <v>3025</v>
+      </c>
+      <c r="E161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>885</v>
+      </c>
+      <c r="B162" t="s">
+        <v>3044</v>
+      </c>
+      <c r="C162" t="s">
+        <v>3045</v>
+      </c>
+      <c r="D162" t="s">
+        <v>3046</v>
+      </c>
+      <c r="E162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>885</v>
+      </c>
+      <c r="B163" t="s">
+        <v>3047</v>
+      </c>
+      <c r="C163" t="s">
+        <v>3048</v>
+      </c>
+      <c r="D163" t="s">
+        <v>3023</v>
+      </c>
+      <c r="E163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>885</v>
+      </c>
+      <c r="B164" t="s">
+        <v>3049</v>
+      </c>
+      <c r="C164" t="s">
+        <v>3050</v>
+      </c>
+      <c r="D164" t="s">
+        <v>3051</v>
+      </c>
+      <c r="E164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>885</v>
+      </c>
+      <c r="B165" t="s">
+        <v>3052</v>
+      </c>
+      <c r="C165" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D165" t="s">
+        <v>3003</v>
+      </c>
+      <c r="E165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>885</v>
+      </c>
+      <c r="B166" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C166" t="s">
+        <v>3054</v>
+      </c>
+      <c r="D166" t="s">
+        <v>3055</v>
+      </c>
+      <c r="E166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>885</v>
+      </c>
+      <c r="B167" t="s">
+        <v>2918</v>
+      </c>
+      <c r="C167" t="s">
+        <v>2994</v>
+      </c>
+      <c r="D167" t="s">
+        <v>3046</v>
+      </c>
+      <c r="E167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>885</v>
+      </c>
+      <c r="B168" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C168" t="s">
+        <v>3056</v>
+      </c>
+      <c r="D168" t="s">
+        <v>3057</v>
+      </c>
+      <c r="E168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>885</v>
+      </c>
+      <c r="B169" t="s">
+        <v>3058</v>
+      </c>
+      <c r="C169" t="s">
+        <v>3059</v>
+      </c>
+      <c r="D169" t="s">
+        <v>3060</v>
+      </c>
+      <c r="E169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>885</v>
+      </c>
+      <c r="B170" t="s">
+        <v>3061</v>
+      </c>
+      <c r="C170" t="s">
+        <v>3062</v>
+      </c>
+      <c r="D170" t="s">
+        <v>2843</v>
+      </c>
+      <c r="E170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>885</v>
+      </c>
+      <c r="B171" t="s">
+        <v>3063</v>
+      </c>
+      <c r="C171" t="s">
+        <v>3008</v>
+      </c>
+      <c r="D171" t="s">
+        <v>3051</v>
+      </c>
+      <c r="E171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>885</v>
+      </c>
+      <c r="B172" t="s">
+        <v>3064</v>
+      </c>
+      <c r="C172" t="s">
+        <v>3065</v>
+      </c>
+      <c r="D172" t="s">
+        <v>3003</v>
+      </c>
+      <c r="E172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>885</v>
+      </c>
+      <c r="B173" t="s">
+        <v>2759</v>
+      </c>
+      <c r="C173" t="s">
+        <v>3066</v>
+      </c>
+      <c r="D173" t="s">
+        <v>3051</v>
+      </c>
+      <c r="E173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>885</v>
+      </c>
+      <c r="B174" t="s">
+        <v>3067</v>
+      </c>
+      <c r="C174" t="s">
+        <v>3039</v>
+      </c>
+      <c r="D174" t="s">
+        <v>3016</v>
+      </c>
+      <c r="E174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>885</v>
+      </c>
+      <c r="B175" t="s">
+        <v>3068</v>
+      </c>
+      <c r="C175" t="s">
+        <v>3069</v>
+      </c>
+      <c r="D175" t="s">
+        <v>3051</v>
+      </c>
+      <c r="E175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>885</v>
+      </c>
+      <c r="B176" t="s">
+        <v>3002</v>
+      </c>
+      <c r="C176" t="s">
+        <v>3070</v>
+      </c>
+      <c r="D176" t="s">
+        <v>3003</v>
+      </c>
+      <c r="E176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>885</v>
+      </c>
+      <c r="B177" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C177" t="s">
+        <v>3071</v>
+      </c>
+      <c r="D177" t="s">
+        <v>3025</v>
+      </c>
+      <c r="E177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>885</v>
+      </c>
+      <c r="B178" t="s">
+        <v>3072</v>
+      </c>
+      <c r="C178" t="s">
+        <v>3073</v>
+      </c>
+      <c r="D178" t="s">
+        <v>3051</v>
+      </c>
+      <c r="E178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>885</v>
+      </c>
+      <c r="B179" t="s">
+        <v>3074</v>
+      </c>
+      <c r="C179" t="s">
+        <v>3034</v>
+      </c>
+      <c r="D179" t="s">
+        <v>3075</v>
+      </c>
+      <c r="E179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>885</v>
+      </c>
+      <c r="B180" t="s">
+        <v>3076</v>
+      </c>
+      <c r="C180" t="s">
+        <v>3077</v>
+      </c>
+      <c r="D180" t="s">
+        <v>3003</v>
+      </c>
+      <c r="E180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>885</v>
+      </c>
+      <c r="B181" t="s">
+        <v>3078</v>
+      </c>
+      <c r="C181" t="s">
+        <v>3079</v>
+      </c>
+      <c r="D181" t="s">
+        <v>3027</v>
+      </c>
+      <c r="E181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>885</v>
+      </c>
+      <c r="B182" t="s">
+        <v>3080</v>
+      </c>
+      <c r="C182" t="s">
+        <v>3081</v>
+      </c>
+      <c r="D182" t="s">
+        <v>3051</v>
+      </c>
+      <c r="E182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>885</v>
+      </c>
+      <c r="B183" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C183" t="s">
+        <v>3082</v>
+      </c>
+      <c r="D183" t="s">
+        <v>3025</v>
+      </c>
+      <c r="E183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>885</v>
+      </c>
+      <c r="B184" t="s">
+        <v>3083</v>
+      </c>
+      <c r="C184" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D184" t="s">
+        <v>3051</v>
+      </c>
+      <c r="E184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>885</v>
+      </c>
+      <c r="B185" t="s">
+        <v>2851</v>
+      </c>
+      <c r="C185" t="s">
+        <v>863</v>
+      </c>
+      <c r="D185" t="s">
+        <v>3003</v>
+      </c>
+      <c r="E185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>885</v>
+      </c>
+      <c r="B186" t="s">
+        <v>3084</v>
+      </c>
+      <c r="C186" t="s">
+        <v>3085</v>
+      </c>
+      <c r="D186" t="s">
+        <v>3086</v>
+      </c>
+      <c r="E186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>885</v>
+      </c>
+      <c r="B187" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C187" t="s">
+        <v>3056</v>
+      </c>
+      <c r="D187" t="s">
+        <v>3057</v>
+      </c>
+      <c r="E187">
         <v>1</v>
       </c>
     </row>

--- a/crit_fails.xlsx
+++ b/crit_fails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srb\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A630CA-7226-47C6-B24A-1B8A9EFA1B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E049AE8F-BA50-4E81-8C14-C596D5E01AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="33465" windowHeight="19545" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11301" uniqueCount="3087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11305" uniqueCount="3089">
   <si>
     <t>attack_type</t>
   </si>
@@ -9288,6 +9288,12 @@
   </si>
   <si>
     <t>Bolí to.</t>
+  </si>
+  <si>
+    <t>Legendary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umřel jsi </t>
   </si>
 </sst>
 </file>
@@ -17265,7 +17271,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80CAE411-9ABA-4D2F-A12C-49D9B350EB7D}">
-  <dimension ref="A1:E187"/>
+  <dimension ref="A1:E188"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
@@ -20454,6 +20460,23 @@
         <v>3057</v>
       </c>
       <c r="E187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>3087</v>
+      </c>
+      <c r="B188" t="s">
+        <v>3088</v>
+      </c>
+      <c r="C188" t="s">
+        <v>3088</v>
+      </c>
+      <c r="D188" t="s">
+        <v>3088</v>
+      </c>
+      <c r="E188">
         <v>1</v>
       </c>
     </row>
